--- a/data/hex_xlsx/KEMIRA.HE.xlsx
+++ b/data/hex_xlsx/KEMIRA.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="540">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1081,6 +1081,12 @@
   </si>
   <si>
     <t>Interest-Bearing Liabilities</t>
+  </si>
+  <si>
+    <t>Loans from financial institutions LT</t>
+  </si>
+  <si>
+    <t>Bonds LT</t>
   </si>
   <si>
     <t>Interest bearing - other non-current liabilities</t>
@@ -1770,7 +1776,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1858,6 +1864,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -18143,12 +18152,30 @@
       <c r="P75" s="17">
         <v>5075.27</v>
       </c>
-      <c r="Q75" s="15"/>
-      <c r="R75" s="15"/>
-      <c r="S75" s="15"/>
-      <c r="T75" s="15"/>
-      <c r="U75" s="15"/>
-      <c r="V75" s="15"/>
+      <c r="Q75" s="17">
+        <f t="shared" ref="Q75:V75" si="1">Q76+Q80+Q83+Q88+Q91</f>
+        <v>5149.33</v>
+      </c>
+      <c r="R75" s="17">
+        <f t="shared" si="1"/>
+        <v>6316.58</v>
+      </c>
+      <c r="S75" s="17">
+        <f t="shared" si="1"/>
+        <v>7433.53</v>
+      </c>
+      <c r="T75" s="17">
+        <f t="shared" si="1"/>
+        <v>7804.18</v>
+      </c>
+      <c r="U75" s="17">
+        <f t="shared" si="1"/>
+        <v>8118.66</v>
+      </c>
+      <c r="V75" s="17">
+        <f t="shared" si="1"/>
+        <v>6774.71</v>
+      </c>
       <c r="W75" s="17">
         <v>3373.4</v>
       </c>
@@ -22026,8 +22053,8 @@
       <c r="AC137" s="15"/>
     </row>
     <row r="138" ht="15.0" customHeight="1">
-      <c r="A138" s="14" t="s">
-        <v>329</v>
+      <c r="A138" s="30" t="s">
+        <v>354</v>
       </c>
       <c r="B138" s="17">
         <v>3310.28</v>
@@ -22113,8 +22140,8 @@
       </c>
     </row>
     <row r="139" ht="15.0" customHeight="1">
-      <c r="A139" s="14" t="s">
-        <v>330</v>
+      <c r="A139" s="30" t="s">
+        <v>355</v>
       </c>
       <c r="B139" s="17">
         <v>2323.82</v>
@@ -22236,7 +22263,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B141" s="17">
         <v>193.75</v>
@@ -22323,7 +22350,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B142" s="16">
         <v>1.18</v>
@@ -22364,7 +22391,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B143" s="17">
         <v>157.13</v>
@@ -22425,7 +22452,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B144" s="17">
         <v>800.99</v>
@@ -22514,7 +22541,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B145" s="17">
         <v>813.99</v>
@@ -22680,7 +22707,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B147" s="15">
         <v>0.0</v>
@@ -22753,7 +22780,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B148" s="17">
         <v>317.8</v>
@@ -22814,7 +22841,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B149" s="16">
         <v>2.36</v>
@@ -22875,7 +22902,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B150" s="17">
         <v>219.74</v>
@@ -22936,7 +22963,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
@@ -23036,7 +23063,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
@@ -23085,7 +23112,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B154" s="20">
         <v>-1.18</v>
@@ -23126,7 +23153,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="18" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B155" s="22">
         <v>9901.32</v>
@@ -23215,7 +23242,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B156" s="15">
         <v>0.0</v>
@@ -23262,7 +23289,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
@@ -23297,7 +23324,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="18" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B158" s="19">
         <v>16985.0</v>
@@ -23386,7 +23413,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B159" s="17">
         <v>2620.35</v>
@@ -23475,7 +23502,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B160" s="17">
         <v>3046.83</v>
@@ -23564,7 +23591,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B161" s="17">
         <v>1018.37</v>
@@ -23649,7 +23676,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B162" s="17">
         <v>2319.09</v>
@@ -23732,7 +23759,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B163" s="21">
         <v>-1200.3</v>
@@ -23805,7 +23832,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B164" s="20">
         <v>-80.34</v>
@@ -23894,7 +23921,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B165" s="15">
         <v>12098.72</v>
@@ -23983,7 +24010,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
@@ -24028,7 +24055,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B167" s="16">
         <v>1.18</v>
@@ -24069,7 +24096,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="18" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B168" s="19">
         <v>19823.9</v>
@@ -24247,7 +24274,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="18" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B170" s="22">
         <v>213.83</v>
@@ -24336,7 +24363,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="18" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B171" s="19">
         <v>20037.74</v>
@@ -24425,7 +24452,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B172" s="15"/>
       <c r="C172" s="20">
@@ -24464,7 +24491,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="18" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B173" s="19">
         <v>37022.74</v>
@@ -24553,7 +24580,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B174" s="17">
         <v>149.45</v>
@@ -24642,7 +24669,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B175" s="17">
         <v>150.34</v>
@@ -24731,7 +24758,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B176" s="16">
         <v>0.9</v>
@@ -24820,7 +24847,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -24861,7 +24888,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -24938,7 +24965,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
@@ -24973,7 +25000,7 @@
     </row>
     <row r="180" ht="15.0" customHeight="1">
       <c r="A180" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
@@ -25038,7 +25065,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="14" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B181" s="16">
         <v>68.52</v>
@@ -25089,7 +25116,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B182" s="17">
         <v>2323.82</v>
@@ -25146,7 +25173,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="14" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B183" s="17">
         <v>2414.78</v>
@@ -25235,7 +25262,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B184" s="17">
         <v>135.86</v>
@@ -25324,7 +25351,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="14" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B185" s="17">
         <v>181.94</v>
@@ -25413,7 +25440,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B186" s="17">
         <v>772.64</v>
@@ -25498,7 +25525,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B187" s="17">
         <v>374.5</v>
@@ -25577,7 +25604,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B188" s="17">
         <v>323.7</v>
@@ -25624,7 +25651,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B189" s="17">
         <v>248.09</v>
@@ -25671,7 +25698,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B190" s="17">
         <v>178.39</v>
@@ -25718,7 +25745,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B191" s="17">
         <v>152.4</v>
@@ -25797,7 +25824,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B192" s="17">
         <v>861.24</v>
@@ -25876,7 +25903,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
@@ -25951,7 +25978,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B194" s="15"/>
       <c r="C194" s="15"/>
@@ -25992,7 +26019,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
@@ -26039,7 +26066,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B196" s="17">
         <v>4725.6</v>
@@ -26082,7 +26109,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B197" s="17">
         <v>149.45</v>
@@ -26171,7 +26198,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B198" s="16">
         <v>0.9</v>
@@ -26260,7 +26287,7 @@
     </row>
     <row r="199" ht="15.0" customHeight="1">
       <c r="A199" s="14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B199" s="16">
         <v>1.0</v>
@@ -26349,7 +26376,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B200" s="17">
         <v>150.34</v>
@@ -27257,7 +27284,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -27721,88 +27748,88 @@
         <v>50</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AB15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -27896,7 +27923,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -28107,7 +28134,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B21" s="17">
         <v>2477.43</v>
@@ -28192,7 +28219,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -28229,7 +28256,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -28266,7 +28293,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
@@ -28303,7 +28330,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -28409,7 +28436,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B27" s="17">
         <v>283.2</v>
@@ -28480,7 +28507,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B28" s="20">
         <v>-1.17</v>
@@ -28519,7 +28546,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B29" s="16">
         <v>2.34</v>
@@ -28588,7 +28615,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B30" s="17">
         <v>157.98</v>
@@ -28675,7 +28702,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -28728,7 +28755,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B32" s="21">
         <v>-139.26</v>
@@ -28817,7 +28844,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B33" s="17">
         <v>174.37</v>
@@ -28906,7 +28933,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B34" s="21">
         <v>-565.23</v>
@@ -28995,7 +29022,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B35" s="21">
         <v>-528.96</v>
@@ -29040,7 +29067,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -29091,7 +29118,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B37" s="21">
         <v>-380.33</v>
@@ -29170,7 +29197,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B38" s="17">
         <v>141.6</v>
@@ -29219,7 +29246,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -29300,7 +29327,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B40" s="16">
         <v>65.53</v>
@@ -29367,7 +29394,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B41" s="21">
         <v>-717.37</v>
@@ -29456,7 +29483,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -29491,7 +29518,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -29562,7 +29589,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
@@ -29621,7 +29648,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B45" s="16">
         <v>2.34</v>
@@ -29678,7 +29705,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="18" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B46" s="22">
         <v>4425.91</v>
@@ -29767,7 +29794,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B47" s="21">
         <v>-1692.19</v>
@@ -29848,7 +29875,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B48" s="21">
         <v>-2301.9</v>
@@ -29937,7 +29964,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B49" s="15">
         <v>0.0</v>
@@ -29976,7 +30003,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B50" s="17">
         <v>562.89</v>
@@ -30045,7 +30072,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -30120,7 +30147,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -30161,7 +30188,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B53" s="20">
         <v>-40.96</v>
@@ -30250,7 +30277,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -30333,7 +30360,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -30372,7 +30399,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B56" s="16">
         <v>4.68</v>
@@ -30407,7 +30434,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B57" s="16">
         <v>4.68</v>
@@ -30442,7 +30469,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -30489,7 +30516,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15">
@@ -30570,7 +30597,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -30627,7 +30654,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -30686,7 +30713,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -30721,7 +30748,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B63" s="16">
         <v>1.17</v>
@@ -30768,7 +30795,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="18" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B64" s="27">
         <v>-3461.62</v>
@@ -30857,7 +30884,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B65" s="17">
         <v>585.13</v>
@@ -30946,7 +30973,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B66" s="21">
         <v>-1523.67</v>
@@ -31035,7 +31062,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B67" s="16">
         <v>58.51</v>
@@ -31124,7 +31151,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B68" s="21">
         <v>-379.16</v>
@@ -31171,7 +31198,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B69" s="21">
         <v>-303.1</v>
@@ -31206,7 +31233,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
@@ -31245,7 +31272,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B71" s="21">
         <v>-1323.56</v>
@@ -31334,7 +31361,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -31373,7 +31400,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B73" s="21">
         <v>-152.13</v>
@@ -31418,7 +31445,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -31453,7 +31480,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B75" s="21">
         <v>-1126.96</v>
@@ -31488,7 +31515,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -31535,7 +31562,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -31608,7 +31635,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -31647,7 +31674,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -31690,7 +31717,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B80" s="16">
         <v>1.17</v>
@@ -31735,7 +31762,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B81" s="16">
         <v>50.32</v>
@@ -31770,7 +31797,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B82" s="27">
         <v>-4113.45</v>
@@ -31859,7 +31886,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B83" s="21">
         <v>-3147.99</v>
@@ -31920,7 +31947,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B84" s="17">
         <v>2862.53</v>
@@ -32009,7 +32036,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B85" s="20">
         <v>-92.45</v>
@@ -32080,7 +32107,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B86" s="17">
         <v>6133.83</v>
@@ -32169,7 +32196,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="18" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B87" s="27">
         <v>-3241.61</v>
@@ -32258,7 +32285,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
@@ -32313,7 +32340,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -32350,7 +32377,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
@@ -33314,7 +33341,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -33509,13 +33536,13 @@
         <v>45</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -34004,7 +34031,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -34127,3844 +34154,3844 @@
         <v>82</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="30" t="s">
-        <v>487</v>
-      </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="31"/>
-      <c r="AB20" s="31"/>
-      <c r="AC20" s="31"/>
-      <c r="AD20" s="31"/>
-      <c r="AE20" s="31"/>
-      <c r="AF20" s="31"/>
+      <c r="A20" s="31" t="s">
+        <v>489</v>
+      </c>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="32" t="s">
-        <v>487</v>
-      </c>
-      <c r="B21" s="33">
+      <c r="A21" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="B21" s="34">
         <v>40969.88</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="34">
         <v>39323.82</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <v>35377.18</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>31578.18</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>29377.85</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <v>29151.37</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <v>28385.61</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="34">
         <v>22633.33</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="34">
         <v>24560.05</v>
       </c>
-      <c r="K21" s="33">
+      <c r="K21" s="34">
         <v>22983.62</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="34">
         <v>22513.28</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="34">
         <v>18387.47</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="34">
         <v>19663.45</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <v>17467.28</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="34">
         <v>15118.63</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="34">
         <v>18536.68</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="34">
         <v>15188.48</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="34">
         <v>15412.19</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="34">
         <v>18129.9</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="34">
         <v>19212.21</v>
       </c>
-      <c r="V21" s="33">
+      <c r="V21" s="34">
         <v>14507.63</v>
       </c>
-      <c r="W21" s="34">
+      <c r="W21" s="35">
         <v>9214.22</v>
       </c>
-      <c r="X21" s="33">
+      <c r="X21" s="34">
         <v>12518.19</v>
       </c>
-      <c r="Y21" s="34">
+      <c r="Y21" s="35">
         <v>8799.38</v>
       </c>
-      <c r="Z21" s="34">
+      <c r="Z21" s="35">
         <v>8933.13</v>
       </c>
-      <c r="AA21" s="34">
+      <c r="AA21" s="35">
         <v>8258.68</v>
       </c>
-      <c r="AB21" s="33">
+      <c r="AB21" s="34">
         <v>10765.67</v>
       </c>
-      <c r="AC21" s="33">
+      <c r="AC21" s="34">
         <v>11423.32</v>
       </c>
-      <c r="AD21" s="33">
+      <c r="AD21" s="34">
         <v>11686.43</v>
       </c>
-      <c r="AE21" s="33">
+      <c r="AE21" s="34">
         <v>12768.41</v>
       </c>
-      <c r="AF21" s="33"/>
+      <c r="AF21" s="34"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="32" t="s">
-        <v>488</v>
-      </c>
-      <c r="B22" s="33">
+      <c r="A22" s="33" t="s">
+        <v>490</v>
+      </c>
+      <c r="B22" s="34">
         <v>37613.6</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="34">
         <v>35851.07</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <v>33055.04</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <v>29142.02</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <v>26792.04</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <v>27190.82</v>
       </c>
-      <c r="H22" s="33">
+      <c r="H22" s="34">
         <v>24680.09</v>
       </c>
-      <c r="I22" s="33">
+      <c r="I22" s="34">
         <v>23163.46</v>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="34">
         <v>23162.64</v>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="34">
         <v>21154.21</v>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="34">
         <v>21257.52</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="34">
         <v>20078.41</v>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="34">
         <v>18183.25</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="34">
         <v>14874.89</v>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="34">
         <v>15535.04</v>
       </c>
-      <c r="Q22" s="33">
+      <c r="Q22" s="34">
         <v>16232.34</v>
       </c>
-      <c r="R22" s="33">
+      <c r="R22" s="34">
         <v>16352.75</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="34">
         <v>17757.38</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="34">
         <v>14349.9</v>
       </c>
-      <c r="U22" s="33">
+      <c r="U22" s="34">
         <v>13114.8</v>
       </c>
-      <c r="V22" s="33">
+      <c r="V22" s="34">
         <v>10792.2</v>
       </c>
-      <c r="W22" s="34">
+      <c r="W22" s="35">
         <v>9788.23</v>
       </c>
-      <c r="X22" s="33">
+      <c r="X22" s="34">
         <v>10335.25</v>
       </c>
-      <c r="Y22" s="34">
+      <c r="Y22" s="35">
         <v>8642.74</v>
       </c>
-      <c r="Z22" s="34">
+      <c r="Z22" s="35">
         <v>9837.4</v>
       </c>
-      <c r="AA22" s="33">
+      <c r="AA22" s="34">
         <v>10963.37</v>
       </c>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="33"/>
-      <c r="AD22" s="33"/>
-      <c r="AE22" s="33"/>
-      <c r="AF22" s="33"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="34"/>
+      <c r="AD22" s="34"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="34"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="31"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="31"/>
-      <c r="T23" s="31"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="31"/>
-      <c r="AC23" s="31"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="31"/>
-      <c r="AF23" s="31"/>
+      <c r="A23" s="31" t="s">
+        <v>491</v>
+      </c>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
+      <c r="AD23" s="32"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="32" t="s">
-        <v>489</v>
-      </c>
-      <c r="B24" s="33">
+      <c r="A24" s="33" t="s">
+        <v>491</v>
+      </c>
+      <c r="B24" s="34">
         <v>34776.98</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="34">
         <v>35680.78</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <v>29172.84</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="34">
         <v>23338.6</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="34">
         <v>20730.94</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <v>21058.52</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="34">
         <v>20270.07</v>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="34">
         <v>15159.97</v>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="34">
         <v>17587.73</v>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="34">
         <v>17109.7</v>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="34">
         <v>16225.26</v>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="34">
         <v>13879.77</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="34">
         <v>15750.38</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <v>13465.61</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="34">
         <v>11032.88</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="34">
         <v>14154.46</v>
       </c>
-      <c r="R24" s="34">
+      <c r="R24" s="35">
         <v>9397.73</v>
       </c>
-      <c r="S24" s="34">
+      <c r="S24" s="35">
         <v>5062.34</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="34">
         <v>10022.85</v>
       </c>
-      <c r="U24" s="33">
+      <c r="U24" s="34">
         <v>12282.85</v>
       </c>
-      <c r="V24" s="34">
+      <c r="V24" s="35">
         <v>9428.79</v>
       </c>
-      <c r="W24" s="34">
+      <c r="W24" s="35">
         <v>7312.1</v>
       </c>
-      <c r="X24" s="34">
+      <c r="X24" s="35">
         <v>5855.02</v>
       </c>
-      <c r="Y24" s="34">
+      <c r="Y24" s="35">
         <v>3611.41</v>
       </c>
-      <c r="Z24" s="34">
+      <c r="Z24" s="35">
         <v>4016.07</v>
       </c>
-      <c r="AA24" s="34">
+      <c r="AA24" s="35">
         <v>3560.39</v>
       </c>
-      <c r="AB24" s="34">
+      <c r="AB24" s="35">
         <v>3897.09</v>
       </c>
-      <c r="AC24" s="34">
+      <c r="AC24" s="35">
         <v>4381.51</v>
       </c>
-      <c r="AD24" s="34">
+      <c r="AD24" s="35">
         <v>5599.43</v>
       </c>
-      <c r="AE24" s="34">
+      <c r="AE24" s="35">
         <v>6284.73</v>
       </c>
-      <c r="AF24" s="34">
+      <c r="AF24" s="35">
         <v>3722.17</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="32" t="s">
-        <v>490</v>
-      </c>
-      <c r="B25" s="33">
+      <c r="A25" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="B25" s="34">
         <v>30435.18</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="34">
         <v>28116.89</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="34">
         <v>24551.05</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="34">
         <v>20752.3</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <v>18936.23</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="34">
         <v>19424.61</v>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="34">
         <v>17616.31</v>
       </c>
-      <c r="I25" s="33">
+      <c r="I25" s="34">
         <v>16697.52</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="34">
         <v>17298.68</v>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="34">
         <v>16041.93</v>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="34">
         <v>16080.61</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="34">
         <v>15370.95</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="34">
         <v>13508.08</v>
       </c>
-      <c r="O25" s="34">
+      <c r="O25" s="35">
         <v>9883.37</v>
       </c>
-      <c r="P25" s="34">
+      <c r="P25" s="35">
         <v>9535.07</v>
       </c>
-      <c r="Q25" s="34">
+      <c r="Q25" s="35">
         <v>9703.01</v>
       </c>
-      <c r="R25" s="34">
+      <c r="R25" s="35">
         <v>9277.46</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="34">
         <v>10382.88</v>
       </c>
-      <c r="T25" s="34">
+      <c r="T25" s="35">
         <v>8758.92</v>
       </c>
-      <c r="U25" s="34">
+      <c r="U25" s="35">
         <v>7823.48</v>
       </c>
-      <c r="V25" s="34">
+      <c r="V25" s="35">
         <v>6015.16</v>
       </c>
-      <c r="W25" s="34">
+      <c r="W25" s="35">
         <v>4970.56</v>
       </c>
-      <c r="X25" s="34">
+      <c r="X25" s="35">
         <v>4385.23</v>
       </c>
-      <c r="Y25" s="34">
+      <c r="Y25" s="35">
         <v>3497.23</v>
       </c>
-      <c r="Z25" s="34">
+      <c r="Z25" s="35">
         <v>4140.74</v>
       </c>
-      <c r="AA25" s="34">
+      <c r="AA25" s="35">
         <v>4747.9</v>
       </c>
-      <c r="AB25" s="34">
+      <c r="AB25" s="35">
         <v>4684.62</v>
       </c>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="33"/>
-      <c r="AE25" s="33"/>
-      <c r="AF25" s="33"/>
+      <c r="AC25" s="34"/>
+      <c r="AD25" s="34"/>
+      <c r="AE25" s="34"/>
+      <c r="AF25" s="34"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="30" t="s">
-        <v>491</v>
-      </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
+      <c r="A26" s="31" t="s">
+        <v>493</v>
+      </c>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="32"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="32" t="s">
-        <v>492</v>
-      </c>
-      <c r="B27" s="34">
+      <c r="A27" s="33" t="s">
+        <v>494</v>
+      </c>
+      <c r="B27" s="35">
         <v>231.32</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>229.69</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <v>187.8</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <v>150.24</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <v>133.45</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <v>135.56</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="35">
         <v>130.49</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="36">
         <v>97.59</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="35">
         <v>113.22</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="35">
         <v>110.14</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="35">
         <v>104.45</v>
       </c>
-      <c r="M27" s="35">
+      <c r="M27" s="36">
         <v>89.35</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>101.39</v>
       </c>
-      <c r="O27" s="35">
+      <c r="O27" s="36">
         <v>86.68</v>
       </c>
-      <c r="P27" s="35">
+      <c r="P27" s="36">
         <v>71.02</v>
       </c>
-      <c r="Q27" s="35">
+      <c r="Q27" s="36">
         <v>91.12</v>
       </c>
-      <c r="R27" s="35">
+      <c r="R27" s="36">
         <v>60.5</v>
       </c>
-      <c r="S27" s="35">
+      <c r="S27" s="36">
         <v>36.8</v>
       </c>
-      <c r="T27" s="35">
+      <c r="T27" s="36">
         <v>72.87</v>
       </c>
-      <c r="U27" s="35">
+      <c r="U27" s="36">
         <v>89.39</v>
       </c>
-      <c r="V27" s="35">
+      <c r="V27" s="36">
         <v>68.69</v>
       </c>
-      <c r="W27" s="35">
+      <c r="W27" s="36">
         <v>53.42</v>
       </c>
-      <c r="X27" s="35">
+      <c r="X27" s="36">
         <v>43.5</v>
       </c>
-      <c r="Y27" s="35">
+      <c r="Y27" s="36">
         <v>26.83</v>
       </c>
-      <c r="Z27" s="35">
+      <c r="Z27" s="36">
         <v>29.84</v>
       </c>
-      <c r="AA27" s="35">
+      <c r="AA27" s="36">
         <v>25.13</v>
       </c>
-      <c r="AB27" s="35">
+      <c r="AB27" s="36">
         <v>27.51</v>
       </c>
-      <c r="AC27" s="35">
+      <c r="AC27" s="36">
         <v>30.93</v>
       </c>
-      <c r="AD27" s="35">
+      <c r="AD27" s="36">
         <v>39.52</v>
       </c>
-      <c r="AE27" s="35">
+      <c r="AE27" s="36">
         <v>44.36</v>
       </c>
-      <c r="AF27" s="35">
+      <c r="AF27" s="36">
         <v>28.01</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="32" t="s">
-        <v>493</v>
-      </c>
-      <c r="B28" s="34">
+      <c r="A28" s="33" t="s">
+        <v>495</v>
+      </c>
+      <c r="B28" s="35">
         <v>197.41</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="35">
         <v>181.0</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="35">
         <v>158.04</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="35">
         <v>133.59</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="35">
         <v>121.9</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="35">
         <v>125.04</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="35">
         <v>113.4</v>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="35">
         <v>107.49</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="35">
         <v>111.36</v>
       </c>
-      <c r="K28" s="34">
+      <c r="K28" s="35">
         <v>103.27</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="35">
         <v>103.52</v>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="36">
         <v>98.95</v>
       </c>
-      <c r="N28" s="35">
+      <c r="N28" s="36">
         <v>86.96</v>
       </c>
-      <c r="O28" s="35">
+      <c r="O28" s="36">
         <v>64.26</v>
       </c>
-      <c r="P28" s="35">
+      <c r="P28" s="36">
         <v>63.68</v>
       </c>
-      <c r="Q28" s="35">
+      <c r="Q28" s="36">
         <v>66.73</v>
       </c>
-      <c r="R28" s="35">
+      <c r="R28" s="36">
         <v>65.93</v>
       </c>
-      <c r="S28" s="35">
+      <c r="S28" s="36">
         <v>75.6</v>
       </c>
-      <c r="T28" s="35">
+      <c r="T28" s="36">
         <v>63.95</v>
       </c>
-      <c r="U28" s="35">
+      <c r="U28" s="36">
         <v>57.29</v>
       </c>
-      <c r="V28" s="35">
+      <c r="V28" s="36">
         <v>44.24</v>
       </c>
-      <c r="W28" s="35">
+      <c r="W28" s="36">
         <v>36.48</v>
       </c>
-      <c r="X28" s="35">
+      <c r="X28" s="36">
         <v>32.01</v>
       </c>
-      <c r="Y28" s="35">
+      <c r="Y28" s="36">
         <v>25.22</v>
       </c>
-      <c r="Z28" s="35">
+      <c r="Z28" s="36">
         <v>29.52</v>
       </c>
-      <c r="AA28" s="35">
+      <c r="AA28" s="36">
         <v>33.51</v>
       </c>
-      <c r="AB28" s="35">
+      <c r="AB28" s="36">
         <v>33.41</v>
       </c>
-      <c r="AC28" s="33"/>
-      <c r="AD28" s="33"/>
-      <c r="AE28" s="33"/>
-      <c r="AF28" s="33"/>
+      <c r="AC28" s="34"/>
+      <c r="AD28" s="34"/>
+      <c r="AE28" s="34"/>
+      <c r="AF28" s="34"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="30" t="s">
-        <v>494</v>
-      </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-      <c r="Q29" s="31"/>
-      <c r="R29" s="31"/>
-      <c r="S29" s="31"/>
-      <c r="T29" s="31"/>
-      <c r="U29" s="31"/>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="31"/>
-      <c r="Y29" s="31"/>
-      <c r="Z29" s="31"/>
-      <c r="AA29" s="31"/>
-      <c r="AB29" s="31"/>
-      <c r="AC29" s="31"/>
-      <c r="AD29" s="31"/>
-      <c r="AE29" s="31"/>
-      <c r="AF29" s="31"/>
+      <c r="A29" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="32" t="s">
-        <v>495</v>
-      </c>
-      <c r="B30" s="36">
+      <c r="A30" s="33" t="s">
+        <v>497</v>
+      </c>
+      <c r="B30" s="37">
         <v>5.9</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>10.47</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="37">
         <v>13.1</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="37">
         <v>9.16</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="37">
         <v>2.51</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>9.02</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>9.12</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>3.97</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <v>1.07</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>3.13</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>4.23</v>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="38">
         <v>-4.45</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>3.54</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="37">
         <v>2.37</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="37">
         <v>5.68</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="37">
         <v>3.26</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="37">
         <v>21.02</v>
       </c>
-      <c r="S30" s="37">
+      <c r="S30" s="38">
         <v>-12.01</v>
       </c>
-      <c r="T30" s="37">
+      <c r="T30" s="38">
         <v>-6.04</v>
       </c>
-      <c r="U30" s="37">
+      <c r="U30" s="38">
         <v>-18.55</v>
       </c>
-      <c r="V30" s="37">
+      <c r="V30" s="38">
         <v>-21.18</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>13.45</v>
       </c>
-      <c r="X30" s="36">
+      <c r="X30" s="37">
         <v>9.81</v>
       </c>
-      <c r="Y30" s="36">
+      <c r="Y30" s="37">
         <v>22.14</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="38">
         <v>-10.68</v>
       </c>
-      <c r="AA30" s="36">
+      <c r="AA30" s="37">
         <v>7.25</v>
       </c>
-      <c r="AB30" s="36">
+      <c r="AB30" s="37">
         <v>5.57</v>
       </c>
-      <c r="AC30" s="37">
+      <c r="AC30" s="38">
         <v>-9.86</v>
       </c>
-      <c r="AD30" s="36">
+      <c r="AD30" s="37">
         <v>6.65</v>
       </c>
-      <c r="AE30" s="36"/>
-      <c r="AF30" s="36"/>
+      <c r="AE30" s="37"/>
+      <c r="AF30" s="37"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="32" t="s">
-        <v>496</v>
-      </c>
-      <c r="B31" s="36">
+      <c r="A31" s="33" t="s">
+        <v>498</v>
+      </c>
+      <c r="B31" s="37">
         <v>8.43</v>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="37">
         <v>9.18</v>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="37">
         <v>8.81</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="37">
         <v>6.93</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="37">
         <v>5.3</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="37">
         <v>5.48</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <v>4.45</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>1.69</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>1.69</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>1.95</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="37">
         <v>2.32</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <v>2.14</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <v>6.03</v>
       </c>
-      <c r="O31" s="36">
+      <c r="O31" s="37">
         <v>5.16</v>
       </c>
-      <c r="P31" s="36">
+      <c r="P31" s="37">
         <v>3.46</v>
       </c>
-      <c r="Q31" s="37">
+      <c r="Q31" s="38">
         <v>-2.6</v>
       </c>
-      <c r="R31" s="37">
+      <c r="R31" s="38">
         <v>-8.34</v>
       </c>
-      <c r="S31" s="37">
+      <c r="S31" s="38">
         <v>-10.21</v>
       </c>
-      <c r="T31" s="37">
+      <c r="T31" s="38">
         <v>-7.47</v>
       </c>
-      <c r="U31" s="37">
+      <c r="U31" s="38">
         <v>-4.71</v>
       </c>
-      <c r="V31" s="37">
+      <c r="V31" s="38">
         <v>-0.09</v>
       </c>
-      <c r="W31" s="36">
+      <c r="W31" s="37">
         <v>9.11</v>
       </c>
-      <c r="X31" s="36">
+      <c r="X31" s="37">
         <v>7.0</v>
       </c>
-      <c r="Y31" s="36">
+      <c r="Y31" s="37">
         <v>2.8</v>
       </c>
-      <c r="Z31" s="37">
+      <c r="Z31" s="38">
         <v>-0.03</v>
       </c>
-      <c r="AA31" s="36"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="36"/>
-      <c r="AD31" s="36"/>
-      <c r="AE31" s="36"/>
-      <c r="AF31" s="36"/>
+      <c r="AA31" s="37"/>
+      <c r="AB31" s="37"/>
+      <c r="AC31" s="37"/>
+      <c r="AD31" s="37"/>
+      <c r="AE31" s="37"/>
+      <c r="AF31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="30" t="s">
-        <v>497</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="31"/>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="31"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31"/>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="31"/>
-      <c r="AE32" s="31"/>
-      <c r="AF32" s="31"/>
+      <c r="A32" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="32"/>
+      <c r="AE32" s="32"/>
+      <c r="AF32" s="32"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="32" t="s">
-        <v>498</v>
-      </c>
-      <c r="B33" s="36">
+      <c r="A33" s="33" t="s">
+        <v>500</v>
+      </c>
+      <c r="B33" s="37">
         <v>3.78</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <v>3.48</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="37">
         <v>3.69</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="37">
         <v>4.05</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="37">
         <v>4.35</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="37">
         <v>4.33</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <v>4.0</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="37">
         <v>5.38</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="37">
         <v>4.61</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <v>4.37</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="37">
         <v>4.87</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="37">
         <v>5.36</v>
       </c>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="36">
+      <c r="N33" s="37"/>
+      <c r="O33" s="37"/>
+      <c r="P33" s="37">
         <v>4.2</v>
       </c>
-      <c r="Q33" s="36">
+      <c r="Q33" s="37">
         <v>1.86</v>
       </c>
-      <c r="R33" s="36">
+      <c r="R33" s="37">
         <v>2.51</v>
       </c>
-      <c r="S33" s="36">
+      <c r="S33" s="37">
         <v>9.64</v>
       </c>
-      <c r="T33" s="36">
+      <c r="T33" s="37">
         <v>3.82</v>
       </c>
-      <c r="U33" s="36">
+      <c r="U33" s="37">
         <v>2.42</v>
       </c>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36">
+      <c r="V33" s="37"/>
+      <c r="W33" s="37">
         <v>5.24</v>
       </c>
-      <c r="X33" s="36">
+      <c r="X33" s="37">
         <v>5.26</v>
       </c>
-      <c r="Y33" s="36">
+      <c r="Y33" s="37">
         <v>7.39</v>
       </c>
-      <c r="Z33" s="36">
+      <c r="Z33" s="37">
         <v>7.28</v>
       </c>
-      <c r="AA33" s="36">
+      <c r="AA33" s="37">
         <v>6.87</v>
       </c>
-      <c r="AB33" s="36">
+      <c r="AB33" s="37">
         <v>7.74</v>
       </c>
-      <c r="AC33" s="36">
+      <c r="AC33" s="37">
         <v>7.52</v>
       </c>
-      <c r="AD33" s="36">
+      <c r="AD33" s="37">
         <v>5.01</v>
       </c>
-      <c r="AE33" s="36">
+      <c r="AE33" s="37">
         <v>4.17</v>
       </c>
-      <c r="AF33" s="36">
+      <c r="AF33" s="37">
         <v>1.77</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="32" t="s">
-        <v>499</v>
-      </c>
-      <c r="B34" s="36">
+      <c r="A34" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="B34" s="37">
         <v>3.83</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <v>3.93</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="37">
         <v>4.06</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="37">
         <v>4.36</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="37">
         <v>4.48</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="37">
         <v>4.49</v>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <v>4.6</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="37">
         <v>4.89</v>
       </c>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36">
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="37"/>
+      <c r="P34" s="37">
         <v>3.65</v>
       </c>
-      <c r="Q34" s="36">
+      <c r="Q34" s="37">
         <v>3.22</v>
       </c>
-      <c r="R34" s="36"/>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36">
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="37">
         <v>6.17</v>
       </c>
-      <c r="X34" s="36">
+      <c r="X34" s="37">
         <v>6.77</v>
       </c>
-      <c r="Y34" s="36">
+      <c r="Y34" s="37">
         <v>7.37</v>
       </c>
-      <c r="Z34" s="36">
+      <c r="Z34" s="37">
         <v>6.74</v>
       </c>
-      <c r="AA34" s="36">
+      <c r="AA34" s="37">
         <v>5.95</v>
       </c>
-      <c r="AB34" s="36">
+      <c r="AB34" s="37">
         <v>5.12</v>
       </c>
-      <c r="AC34" s="36"/>
-      <c r="AD34" s="36"/>
-      <c r="AE34" s="36"/>
-      <c r="AF34" s="36"/>
+      <c r="AC34" s="37"/>
+      <c r="AD34" s="37"/>
+      <c r="AE34" s="37"/>
+      <c r="AF34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="32" t="s">
-        <v>500</v>
-      </c>
-      <c r="B35" s="36">
+      <c r="A35" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="B35" s="37">
         <v>3.78</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <v>3.48</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="37">
         <v>3.69</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <v>4.05</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="37">
         <v>4.35</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <v>4.33</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <v>4.0</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="37">
         <v>5.38</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="37">
         <v>4.61</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="37">
         <v>4.37</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <v>4.87</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <v>5.36</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <v>4.36</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="37">
         <v>4.49</v>
       </c>
-      <c r="P35" s="36">
+      <c r="P35" s="37">
         <v>5.23</v>
       </c>
-      <c r="Q35" s="36">
+      <c r="Q35" s="37">
         <v>2.31</v>
       </c>
-      <c r="R35" s="36">
+      <c r="R35" s="37">
         <v>3.12</v>
       </c>
-      <c r="S35" s="36">
+      <c r="S35" s="37">
         <v>11.99</v>
       </c>
-      <c r="T35" s="36">
+      <c r="T35" s="37">
         <v>4.75</v>
       </c>
-      <c r="U35" s="36">
+      <c r="U35" s="37">
         <v>3.01</v>
       </c>
-      <c r="V35" s="36">
+      <c r="V35" s="37">
         <v>3.59</v>
       </c>
-      <c r="W35" s="36">
+      <c r="W35" s="37">
         <v>4.63</v>
       </c>
-      <c r="X35" s="36">
+      <c r="X35" s="37">
         <v>5.26</v>
       </c>
-      <c r="Y35" s="36">
+      <c r="Y35" s="37">
         <v>7.39</v>
       </c>
-      <c r="Z35" s="36">
+      <c r="Z35" s="37">
         <v>7.28</v>
       </c>
-      <c r="AA35" s="36">
+      <c r="AA35" s="37">
         <v>6.87</v>
       </c>
-      <c r="AB35" s="36">
+      <c r="AB35" s="37">
         <v>7.74</v>
       </c>
-      <c r="AC35" s="36">
+      <c r="AC35" s="37">
         <v>7.52</v>
       </c>
-      <c r="AD35" s="36">
+      <c r="AD35" s="37">
         <v>5.01</v>
       </c>
-      <c r="AE35" s="36">
+      <c r="AE35" s="37">
         <v>4.17</v>
       </c>
-      <c r="AF35" s="36">
+      <c r="AF35" s="37">
         <v>1.77</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="32" t="s">
-        <v>501</v>
-      </c>
-      <c r="B36" s="36">
+      <c r="A36" s="33" t="s">
+        <v>503</v>
+      </c>
+      <c r="B36" s="37">
         <v>3.83</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <v>3.93</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="37">
         <v>4.06</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="37">
         <v>4.36</v>
       </c>
-      <c r="F36" s="36">
+      <c r="F36" s="37">
         <v>4.48</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="37">
         <v>4.49</v>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <v>4.6</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="37">
         <v>4.89</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="37">
         <v>4.69</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="37">
         <v>4.66</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="37">
         <v>4.82</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="37">
         <v>4.28</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="37">
         <v>3.91</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="37">
         <v>4.48</v>
       </c>
-      <c r="P36" s="36">
+      <c r="P36" s="37">
         <v>4.54</v>
       </c>
-      <c r="Q36" s="36">
+      <c r="Q36" s="37">
         <v>4.0</v>
       </c>
-      <c r="R36" s="36">
+      <c r="R36" s="37">
         <v>4.41</v>
       </c>
-      <c r="S36" s="36">
+      <c r="S36" s="37">
         <v>4.69</v>
       </c>
-      <c r="T36" s="36">
+      <c r="T36" s="37">
         <v>4.08</v>
       </c>
-      <c r="U36" s="36">
+      <c r="U36" s="37">
         <v>4.25</v>
       </c>
-      <c r="V36" s="36">
+      <c r="V36" s="37">
         <v>5.15</v>
       </c>
-      <c r="W36" s="36">
+      <c r="W36" s="37">
         <v>5.99</v>
       </c>
-      <c r="X36" s="36">
+      <c r="X36" s="37">
         <v>6.77</v>
       </c>
-      <c r="Y36" s="36">
+      <c r="Y36" s="37">
         <v>7.37</v>
       </c>
-      <c r="Z36" s="36">
+      <c r="Z36" s="37">
         <v>6.74</v>
       </c>
-      <c r="AA36" s="36">
+      <c r="AA36" s="37">
         <v>5.95</v>
       </c>
-      <c r="AB36" s="36">
+      <c r="AB36" s="37">
         <v>5.12</v>
       </c>
-      <c r="AC36" s="36"/>
-      <c r="AD36" s="36"/>
-      <c r="AE36" s="36"/>
-      <c r="AF36" s="36"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="37"/>
+      <c r="AE36" s="37"/>
+      <c r="AF36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="30" t="s">
-        <v>502</v>
-      </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
-      <c r="O37" s="31"/>
-      <c r="P37" s="31"/>
-      <c r="Q37" s="31"/>
-      <c r="R37" s="31"/>
-      <c r="S37" s="31"/>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
-      <c r="X37" s="31"/>
-      <c r="Y37" s="31"/>
-      <c r="Z37" s="31"/>
-      <c r="AA37" s="31"/>
-      <c r="AB37" s="31"/>
-      <c r="AC37" s="31"/>
-      <c r="AD37" s="31"/>
-      <c r="AE37" s="31"/>
-      <c r="AF37" s="31"/>
+      <c r="A37" s="31" t="s">
+        <v>504</v>
+      </c>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="32"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="32"/>
+      <c r="Z37" s="32"/>
+      <c r="AA37" s="32"/>
+      <c r="AB37" s="32"/>
+      <c r="AC37" s="32"/>
+      <c r="AD37" s="32"/>
+      <c r="AE37" s="32"/>
+      <c r="AF37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="32" t="s">
-        <v>503</v>
-      </c>
-      <c r="B38" s="35">
+      <c r="A38" s="33" t="s">
+        <v>505</v>
+      </c>
+      <c r="B38" s="36">
         <v>1.74</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="36">
         <v>1.68</v>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="36">
         <v>1.55</v>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="36">
         <v>1.32</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="36">
         <v>1.54</v>
       </c>
-      <c r="G38" s="35">
+      <c r="G38" s="36">
         <v>1.66</v>
       </c>
-      <c r="H38" s="35">
+      <c r="H38" s="36">
         <v>1.66</v>
       </c>
-      <c r="I38" s="35">
+      <c r="I38" s="36">
         <v>1.26</v>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="36">
         <v>1.51</v>
       </c>
-      <c r="K38" s="35">
+      <c r="K38" s="36">
         <v>1.58</v>
       </c>
-      <c r="L38" s="35">
+      <c r="L38" s="36">
         <v>1.4</v>
       </c>
-      <c r="M38" s="35">
+      <c r="M38" s="36">
         <v>1.31</v>
       </c>
-      <c r="N38" s="35">
+      <c r="N38" s="36">
         <v>1.66</v>
       </c>
-      <c r="O38" s="35">
+      <c r="O38" s="36">
         <v>1.44</v>
       </c>
-      <c r="P38" s="35">
+      <c r="P38" s="36">
         <v>1.03</v>
       </c>
-      <c r="Q38" s="35">
+      <c r="Q38" s="36">
         <v>1.32</v>
       </c>
-      <c r="R38" s="35">
+      <c r="R38" s="36">
         <v>0.88</v>
       </c>
-      <c r="S38" s="35">
+      <c r="S38" s="36">
         <v>0.52</v>
       </c>
-      <c r="T38" s="35">
+      <c r="T38" s="36">
         <v>1.14</v>
       </c>
-      <c r="U38" s="35">
+      <c r="U38" s="36">
         <v>1.35</v>
       </c>
-      <c r="V38" s="35">
+      <c r="V38" s="36">
         <v>1.14</v>
       </c>
-      <c r="W38" s="35">
+      <c r="W38" s="36">
         <v>0.92</v>
       </c>
-      <c r="X38" s="35">
+      <c r="X38" s="36">
         <v>0.65</v>
       </c>
-      <c r="Y38" s="35">
+      <c r="Y38" s="36">
         <v>0.45</v>
       </c>
-      <c r="Z38" s="35">
+      <c r="Z38" s="36">
         <v>0.44</v>
       </c>
-      <c r="AA38" s="35">
+      <c r="AA38" s="36">
         <v>0.37</v>
       </c>
-      <c r="AB38" s="35">
+      <c r="AB38" s="36">
         <v>0.5</v>
       </c>
-      <c r="AC38" s="35">
+      <c r="AC38" s="36">
         <v>0.52</v>
       </c>
-      <c r="AD38" s="35">
+      <c r="AD38" s="36">
         <v>0.75</v>
       </c>
-      <c r="AE38" s="35">
+      <c r="AE38" s="36">
         <v>0.93</v>
       </c>
-      <c r="AF38" s="33"/>
+      <c r="AF38" s="34"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="32" t="s">
-        <v>504</v>
-      </c>
-      <c r="B39" s="35">
+      <c r="A39" s="33" t="s">
+        <v>506</v>
+      </c>
+      <c r="B39" s="36">
         <v>1.57</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="36">
         <v>1.54</v>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="36">
         <v>1.53</v>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="36">
         <v>1.48</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="36">
         <v>1.53</v>
       </c>
-      <c r="G39" s="35">
+      <c r="G39" s="36">
         <v>1.54</v>
       </c>
-      <c r="H39" s="35">
+      <c r="H39" s="36">
         <v>1.48</v>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="36">
         <v>1.41</v>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="36">
         <v>1.49</v>
       </c>
-      <c r="K39" s="35">
+      <c r="K39" s="36">
         <v>1.48</v>
       </c>
-      <c r="L39" s="35">
+      <c r="L39" s="36">
         <v>1.36</v>
       </c>
-      <c r="M39" s="35">
+      <c r="M39" s="36">
         <v>1.34</v>
       </c>
-      <c r="N39" s="35">
+      <c r="N39" s="36">
         <v>1.26</v>
       </c>
-      <c r="O39" s="35">
+      <c r="O39" s="36">
         <v>1.06</v>
       </c>
-      <c r="P39" s="35">
+      <c r="P39" s="36">
         <v>1.0</v>
       </c>
-      <c r="Q39" s="35">
+      <c r="Q39" s="36">
         <v>1.06</v>
       </c>
-      <c r="R39" s="35">
+      <c r="R39" s="36">
         <v>1.02</v>
       </c>
-      <c r="S39" s="35">
+      <c r="S39" s="36">
         <v>1.03</v>
       </c>
-      <c r="T39" s="35">
+      <c r="T39" s="36">
         <v>1.04</v>
       </c>
-      <c r="U39" s="35">
+      <c r="U39" s="36">
         <v>0.9</v>
       </c>
-      <c r="V39" s="35">
+      <c r="V39" s="36">
         <v>0.71</v>
       </c>
-      <c r="W39" s="35">
+      <c r="W39" s="36">
         <v>0.56</v>
       </c>
-      <c r="X39" s="35">
+      <c r="X39" s="36">
         <v>0.48</v>
       </c>
-      <c r="Y39" s="35">
+      <c r="Y39" s="36">
         <v>0.45</v>
       </c>
-      <c r="Z39" s="35">
+      <c r="Z39" s="36">
         <v>0.5</v>
       </c>
-      <c r="AA39" s="35">
+      <c r="AA39" s="36">
         <v>0.59</v>
       </c>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
-      <c r="AD39" s="33"/>
-      <c r="AE39" s="33"/>
-      <c r="AF39" s="33"/>
+      <c r="AB39" s="34"/>
+      <c r="AC39" s="34"/>
+      <c r="AD39" s="34"/>
+      <c r="AE39" s="34"/>
+      <c r="AF39" s="34"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="30" t="s">
-        <v>505</v>
-      </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="31"/>
-      <c r="N40" s="31"/>
-      <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
-      <c r="Q40" s="31"/>
-      <c r="R40" s="31"/>
-      <c r="S40" s="31"/>
-      <c r="T40" s="31"/>
-      <c r="U40" s="31"/>
-      <c r="V40" s="31"/>
-      <c r="W40" s="31"/>
-      <c r="X40" s="31"/>
-      <c r="Y40" s="31"/>
-      <c r="Z40" s="31"/>
-      <c r="AA40" s="31"/>
-      <c r="AB40" s="31"/>
-      <c r="AC40" s="31"/>
-      <c r="AD40" s="31"/>
-      <c r="AE40" s="31"/>
-      <c r="AF40" s="31"/>
+      <c r="A40" s="31" t="s">
+        <v>507</v>
+      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
+      <c r="P40" s="32"/>
+      <c r="Q40" s="32"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="32"/>
+      <c r="T40" s="32"/>
+      <c r="U40" s="32"/>
+      <c r="V40" s="32"/>
+      <c r="W40" s="32"/>
+      <c r="X40" s="32"/>
+      <c r="Y40" s="32"/>
+      <c r="Z40" s="32"/>
+      <c r="AA40" s="32"/>
+      <c r="AB40" s="32"/>
+      <c r="AC40" s="32"/>
+      <c r="AD40" s="32"/>
+      <c r="AE40" s="32"/>
+      <c r="AF40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="32" t="s">
-        <v>506</v>
-      </c>
-      <c r="B41" s="35">
+      <c r="A41" s="33" t="s">
+        <v>508</v>
+      </c>
+      <c r="B41" s="36">
         <v>2.79</v>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="36">
         <v>2.4</v>
       </c>
-      <c r="D41" s="35">
+      <c r="D41" s="36">
         <v>2.28</v>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="36">
         <v>2.0</v>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="36">
         <v>2.73</v>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="36">
         <v>3.24</v>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="36">
         <v>3.34</v>
       </c>
-      <c r="I41" s="35">
+      <c r="I41" s="36">
         <v>2.74</v>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="36">
         <v>3.17</v>
       </c>
-      <c r="K41" s="35">
+      <c r="K41" s="36">
         <v>3.48</v>
       </c>
-      <c r="L41" s="35">
+      <c r="L41" s="36">
         <v>3.14</v>
       </c>
-      <c r="M41" s="35">
+      <c r="M41" s="36">
         <v>2.55</v>
       </c>
-      <c r="N41" s="35">
+      <c r="N41" s="36">
         <v>3.27</v>
       </c>
-      <c r="O41" s="35">
+      <c r="O41" s="36">
         <v>2.7</v>
       </c>
-      <c r="P41" s="35">
+      <c r="P41" s="36">
         <v>2.04</v>
       </c>
-      <c r="Q41" s="35">
+      <c r="Q41" s="36">
         <v>2.7</v>
       </c>
-      <c r="R41" s="35">
+      <c r="R41" s="36">
         <v>2.26</v>
       </c>
-      <c r="S41" s="35">
+      <c r="S41" s="36">
         <v>2.58</v>
       </c>
-      <c r="T41" s="35">
+      <c r="T41" s="36">
         <v>3.68</v>
       </c>
-      <c r="U41" s="35">
+      <c r="U41" s="36">
         <v>3.81</v>
       </c>
-      <c r="V41" s="35">
+      <c r="V41" s="36">
         <v>2.55</v>
       </c>
-      <c r="W41" s="35">
+      <c r="W41" s="36">
         <v>0.92</v>
       </c>
-      <c r="X41" s="35">
+      <c r="X41" s="36">
         <v>0.65</v>
       </c>
-      <c r="Y41" s="35">
+      <c r="Y41" s="36">
         <v>0.45</v>
       </c>
-      <c r="Z41" s="35">
+      <c r="Z41" s="36">
         <v>0.49</v>
       </c>
-      <c r="AA41" s="35">
+      <c r="AA41" s="36">
         <v>0.38</v>
       </c>
-      <c r="AB41" s="35">
+      <c r="AB41" s="36">
         <v>0.56</v>
       </c>
-      <c r="AC41" s="35">
+      <c r="AC41" s="36">
         <v>0.59</v>
       </c>
-      <c r="AD41" s="35">
+      <c r="AD41" s="36">
         <v>0.78</v>
       </c>
-      <c r="AE41" s="35">
+      <c r="AE41" s="36">
         <v>0.94</v>
       </c>
-      <c r="AF41" s="33"/>
+      <c r="AF41" s="34"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="32" t="s">
-        <v>507</v>
-      </c>
-      <c r="B42" s="35">
+      <c r="A42" s="33" t="s">
+        <v>509</v>
+      </c>
+      <c r="B42" s="36">
         <v>2.42</v>
       </c>
-      <c r="C42" s="35">
+      <c r="C42" s="36">
         <v>2.44</v>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="36">
         <v>2.58</v>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="36">
         <v>2.7</v>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="36">
         <v>3.03</v>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="36">
         <v>3.19</v>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="36">
         <v>3.17</v>
       </c>
-      <c r="I42" s="35">
+      <c r="I42" s="36">
         <v>3.0</v>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="36">
         <v>3.11</v>
       </c>
-      <c r="K42" s="35">
+      <c r="K42" s="36">
         <v>3.01</v>
       </c>
-      <c r="L42" s="35">
+      <c r="L42" s="36">
         <v>2.7</v>
       </c>
-      <c r="M42" s="35">
+      <c r="M42" s="36">
         <v>2.63</v>
       </c>
-      <c r="N42" s="35">
+      <c r="N42" s="36">
         <v>2.59</v>
       </c>
-      <c r="O42" s="35">
+      <c r="O42" s="36">
         <v>2.44</v>
       </c>
-      <c r="P42" s="35">
+      <c r="P42" s="36">
         <v>2.57</v>
       </c>
-      <c r="Q42" s="35">
+      <c r="Q42" s="36">
         <v>2.98</v>
       </c>
-      <c r="R42" s="35">
+      <c r="R42" s="36">
         <v>2.96</v>
       </c>
-      <c r="S42" s="35">
+      <c r="S42" s="36">
         <v>2.26</v>
       </c>
-      <c r="T42" s="35">
+      <c r="T42" s="36">
         <v>1.7</v>
       </c>
-      <c r="U42" s="35">
+      <c r="U42" s="36">
         <v>1.19</v>
       </c>
-      <c r="V42" s="35">
+      <c r="V42" s="36">
         <v>0.81</v>
       </c>
-      <c r="W42" s="35">
+      <c r="W42" s="36">
         <v>0.57</v>
       </c>
-      <c r="X42" s="35">
+      <c r="X42" s="36">
         <v>0.5</v>
       </c>
-      <c r="Y42" s="35">
+      <c r="Y42" s="36">
         <v>0.49</v>
       </c>
-      <c r="Z42" s="35">
+      <c r="Z42" s="36">
         <v>0.55</v>
       </c>
-      <c r="AA42" s="35">
+      <c r="AA42" s="36">
         <v>0.63</v>
       </c>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
-      <c r="AD42" s="33"/>
-      <c r="AE42" s="33"/>
-      <c r="AF42" s="33"/>
+      <c r="AB42" s="34"/>
+      <c r="AC42" s="34"/>
+      <c r="AD42" s="34"/>
+      <c r="AE42" s="34"/>
+      <c r="AF42" s="34"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="30" t="s">
-        <v>508</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="31"/>
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="31"/>
-      <c r="Q43" s="31"/>
-      <c r="R43" s="31"/>
-      <c r="S43" s="31"/>
-      <c r="T43" s="31"/>
-      <c r="U43" s="31"/>
-      <c r="V43" s="31"/>
-      <c r="W43" s="31"/>
-      <c r="X43" s="31"/>
-      <c r="Y43" s="31"/>
-      <c r="Z43" s="31"/>
-      <c r="AA43" s="31"/>
-      <c r="AB43" s="31"/>
-      <c r="AC43" s="31"/>
-      <c r="AD43" s="31"/>
-      <c r="AE43" s="31"/>
-      <c r="AF43" s="31"/>
+      <c r="A43" s="31" t="s">
+        <v>510</v>
+      </c>
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="32"/>
+      <c r="Q43" s="32"/>
+      <c r="R43" s="32"/>
+      <c r="S43" s="32"/>
+      <c r="T43" s="32"/>
+      <c r="U43" s="32"/>
+      <c r="V43" s="32"/>
+      <c r="W43" s="32"/>
+      <c r="X43" s="32"/>
+      <c r="Y43" s="32"/>
+      <c r="Z43" s="32"/>
+      <c r="AA43" s="32"/>
+      <c r="AB43" s="32"/>
+      <c r="AC43" s="32"/>
+      <c r="AD43" s="32"/>
+      <c r="AE43" s="32"/>
+      <c r="AF43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="32" t="s">
-        <v>509</v>
-      </c>
-      <c r="B44" s="35">
+      <c r="A44" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="B44" s="36">
         <v>1.1</v>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <v>1.03</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="36">
         <v>0.77</v>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="36">
         <v>0.62</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="36">
         <v>0.77</v>
       </c>
-      <c r="G44" s="35">
+      <c r="G44" s="36">
         <v>0.82</v>
       </c>
-      <c r="H44" s="35">
+      <c r="H44" s="36">
         <v>0.76</v>
       </c>
-      <c r="I44" s="35">
+      <c r="I44" s="36">
         <v>0.58</v>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="36">
         <v>0.71</v>
       </c>
-      <c r="K44" s="35">
+      <c r="K44" s="36">
         <v>0.78</v>
       </c>
-      <c r="L44" s="35">
+      <c r="L44" s="36">
         <v>0.7</v>
       </c>
-      <c r="M44" s="35">
+      <c r="M44" s="36">
         <v>0.7</v>
       </c>
-      <c r="N44" s="35">
+      <c r="N44" s="36">
         <v>0.83</v>
       </c>
-      <c r="O44" s="35">
+      <c r="O44" s="36">
         <v>0.8</v>
       </c>
-      <c r="P44" s="35">
+      <c r="P44" s="36">
         <v>0.63</v>
       </c>
-      <c r="Q44" s="35">
+      <c r="Q44" s="36">
         <v>0.82</v>
       </c>
-      <c r="R44" s="35">
+      <c r="R44" s="36">
         <v>0.5</v>
       </c>
-      <c r="S44" s="35">
+      <c r="S44" s="36">
         <v>0.18</v>
       </c>
-      <c r="T44" s="35">
+      <c r="T44" s="36">
         <v>0.43</v>
       </c>
-      <c r="U44" s="35">
+      <c r="U44" s="36">
         <v>0.51</v>
       </c>
-      <c r="V44" s="35">
+      <c r="V44" s="36">
         <v>0.55</v>
       </c>
-      <c r="W44" s="35">
+      <c r="W44" s="36">
         <v>0.45</v>
       </c>
-      <c r="X44" s="35">
+      <c r="X44" s="36">
         <v>0.25</v>
       </c>
-      <c r="Y44" s="35">
+      <c r="Y44" s="36">
         <v>0.18</v>
       </c>
-      <c r="Z44" s="35">
+      <c r="Z44" s="36">
         <v>0.2</v>
       </c>
-      <c r="AA44" s="35">
+      <c r="AA44" s="36">
         <v>0.17</v>
       </c>
-      <c r="AB44" s="35">
+      <c r="AB44" s="36">
         <v>0.19</v>
       </c>
-      <c r="AC44" s="35">
+      <c r="AC44" s="36">
         <v>0.2</v>
       </c>
-      <c r="AD44" s="35">
+      <c r="AD44" s="36">
         <v>0.28</v>
       </c>
-      <c r="AE44" s="35">
+      <c r="AE44" s="36">
         <v>0.32</v>
       </c>
-      <c r="AF44" s="35">
+      <c r="AF44" s="36">
         <v>0.21</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="32" t="s">
-        <v>510</v>
-      </c>
-      <c r="B45" s="35">
+      <c r="A45" s="33" t="s">
+        <v>512</v>
+      </c>
+      <c r="B45" s="36">
         <v>0.84</v>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="36">
         <v>0.79</v>
       </c>
-      <c r="D45" s="35">
+      <c r="D45" s="36">
         <v>0.74</v>
       </c>
-      <c r="E45" s="35">
+      <c r="E45" s="36">
         <v>0.7</v>
       </c>
-      <c r="F45" s="35">
+      <c r="F45" s="36">
         <v>0.73</v>
       </c>
-      <c r="G45" s="35">
+      <c r="G45" s="36">
         <v>0.73</v>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="36">
         <v>0.71</v>
       </c>
-      <c r="I45" s="35">
+      <c r="I45" s="36">
         <v>0.69</v>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="36">
         <v>0.74</v>
       </c>
-      <c r="K45" s="35">
+      <c r="K45" s="36">
         <v>0.76</v>
       </c>
-      <c r="L45" s="35">
+      <c r="L45" s="36">
         <v>0.73</v>
       </c>
-      <c r="M45" s="35">
+      <c r="M45" s="36">
         <v>0.76</v>
       </c>
-      <c r="N45" s="35">
+      <c r="N45" s="36">
         <v>0.71</v>
       </c>
-      <c r="O45" s="35">
+      <c r="O45" s="36">
         <v>0.55</v>
       </c>
-      <c r="P45" s="35">
+      <c r="P45" s="36">
         <v>0.48</v>
       </c>
-      <c r="Q45" s="35">
+      <c r="Q45" s="36">
         <v>0.46</v>
       </c>
-      <c r="R45" s="35">
+      <c r="R45" s="36">
         <v>0.42</v>
       </c>
-      <c r="S45" s="35">
+      <c r="S45" s="36">
         <v>0.41</v>
       </c>
-      <c r="T45" s="35">
+      <c r="T45" s="36">
         <v>0.43</v>
       </c>
-      <c r="U45" s="35">
+      <c r="U45" s="36">
         <v>0.38</v>
       </c>
-      <c r="V45" s="35">
+      <c r="V45" s="36">
         <v>0.31</v>
       </c>
-      <c r="W45" s="35">
+      <c r="W45" s="36">
         <v>0.24</v>
       </c>
-      <c r="X45" s="35">
+      <c r="X45" s="36">
         <v>0.2</v>
       </c>
-      <c r="Y45" s="35">
+      <c r="Y45" s="36">
         <v>0.19</v>
       </c>
-      <c r="Z45" s="35">
+      <c r="Z45" s="36">
         <v>0.21</v>
       </c>
-      <c r="AA45" s="35">
+      <c r="AA45" s="36">
         <v>0.23</v>
       </c>
-      <c r="AB45" s="35">
+      <c r="AB45" s="36">
         <v>0.24</v>
       </c>
-      <c r="AC45" s="33"/>
-      <c r="AD45" s="33"/>
-      <c r="AE45" s="33"/>
-      <c r="AF45" s="33"/>
+      <c r="AC45" s="34"/>
+      <c r="AD45" s="34"/>
+      <c r="AE45" s="34"/>
+      <c r="AF45" s="34"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="30" t="s">
-        <v>511</v>
-      </c>
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="31"/>
-      <c r="N46" s="31"/>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
-      <c r="W46" s="31"/>
-      <c r="X46" s="31"/>
-      <c r="Y46" s="31"/>
-      <c r="Z46" s="31"/>
-      <c r="AA46" s="31"/>
-      <c r="AB46" s="31"/>
-      <c r="AC46" s="31"/>
-      <c r="AD46" s="31"/>
-      <c r="AE46" s="31"/>
-      <c r="AF46" s="31"/>
+      <c r="A46" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
+      <c r="L46" s="32"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="32"/>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+      <c r="Z46" s="32"/>
+      <c r="AA46" s="32"/>
+      <c r="AB46" s="32"/>
+      <c r="AC46" s="32"/>
+      <c r="AD46" s="32"/>
+      <c r="AE46" s="32"/>
+      <c r="AF46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="32" t="s">
-        <v>512</v>
-      </c>
-      <c r="B47" s="35">
+      <c r="A47" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="B47" s="36">
         <v>16.94</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="36">
         <v>9.55</v>
       </c>
-      <c r="D47" s="35">
+      <c r="D47" s="36">
         <v>7.63</v>
       </c>
-      <c r="E47" s="35">
+      <c r="E47" s="36">
         <v>10.92</v>
       </c>
-      <c r="F47" s="35">
+      <c r="F47" s="36">
         <v>39.88</v>
       </c>
-      <c r="G47" s="35">
+      <c r="G47" s="36">
         <v>11.08</v>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="36">
         <v>10.97</v>
       </c>
-      <c r="I47" s="35">
+      <c r="I47" s="36">
         <v>25.16</v>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="36">
         <v>93.84</v>
       </c>
-      <c r="K47" s="35">
+      <c r="K47" s="36">
         <v>31.9</v>
       </c>
-      <c r="L47" s="35">
+      <c r="L47" s="36">
         <v>23.65</v>
       </c>
-      <c r="M47" s="33"/>
-      <c r="N47" s="35">
+      <c r="M47" s="34"/>
+      <c r="N47" s="36">
         <v>28.23</v>
       </c>
-      <c r="O47" s="35">
+      <c r="O47" s="36">
         <v>42.19</v>
       </c>
-      <c r="P47" s="35">
+      <c r="P47" s="36">
         <v>17.59</v>
       </c>
-      <c r="Q47" s="35">
+      <c r="Q47" s="36">
         <v>30.72</v>
       </c>
-      <c r="R47" s="35">
+      <c r="R47" s="36">
         <v>4.76</v>
       </c>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
-      <c r="V47" s="33"/>
-      <c r="W47" s="35">
+      <c r="S47" s="34"/>
+      <c r="T47" s="34"/>
+      <c r="U47" s="34"/>
+      <c r="V47" s="34"/>
+      <c r="W47" s="36">
         <v>7.44</v>
       </c>
-      <c r="X47" s="35">
+      <c r="X47" s="36">
         <v>10.19</v>
       </c>
-      <c r="Y47" s="35">
+      <c r="Y47" s="36">
         <v>4.52</v>
       </c>
-      <c r="Z47" s="33"/>
-      <c r="AA47" s="35">
+      <c r="Z47" s="34"/>
+      <c r="AA47" s="36">
         <v>13.8</v>
       </c>
-      <c r="AB47" s="35">
+      <c r="AB47" s="36">
         <v>17.95</v>
       </c>
-      <c r="AC47" s="33"/>
-      <c r="AD47" s="35">
+      <c r="AC47" s="34"/>
+      <c r="AD47" s="36">
         <v>15.03</v>
       </c>
-      <c r="AE47" s="33"/>
-      <c r="AF47" s="33"/>
+      <c r="AE47" s="34"/>
+      <c r="AF47" s="34"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="32" t="s">
-        <v>513</v>
-      </c>
-      <c r="B48" s="35">
+      <c r="A48" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="B48" s="36">
         <v>11.86</v>
       </c>
-      <c r="C48" s="35">
+      <c r="C48" s="36">
         <v>10.9</v>
       </c>
-      <c r="D48" s="35">
+      <c r="D48" s="36">
         <v>11.35</v>
       </c>
-      <c r="E48" s="35">
+      <c r="E48" s="36">
         <v>14.43</v>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="36">
         <v>18.88</v>
       </c>
-      <c r="G48" s="35">
+      <c r="G48" s="36">
         <v>18.24</v>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="36">
         <v>22.48</v>
       </c>
-      <c r="I48" s="35">
+      <c r="I48" s="36">
         <v>59.3</v>
       </c>
-      <c r="J48" s="35">
+      <c r="J48" s="36">
         <v>59.28</v>
       </c>
-      <c r="K48" s="35">
+      <c r="K48" s="36">
         <v>51.16</v>
       </c>
-      <c r="L48" s="35">
+      <c r="L48" s="36">
         <v>43.03</v>
       </c>
-      <c r="M48" s="35">
+      <c r="M48" s="36">
         <v>46.63</v>
       </c>
-      <c r="N48" s="35">
+      <c r="N48" s="36">
         <v>16.57</v>
       </c>
-      <c r="O48" s="35">
+      <c r="O48" s="36">
         <v>19.37</v>
       </c>
-      <c r="P48" s="35">
+      <c r="P48" s="36">
         <v>28.87</v>
       </c>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="33"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
-      <c r="V48" s="33"/>
-      <c r="W48" s="35">
+      <c r="Q48" s="34"/>
+      <c r="R48" s="34"/>
+      <c r="S48" s="34"/>
+      <c r="T48" s="34"/>
+      <c r="U48" s="34"/>
+      <c r="V48" s="34"/>
+      <c r="W48" s="36">
         <v>10.98</v>
       </c>
-      <c r="X48" s="35">
+      <c r="X48" s="36">
         <v>14.28</v>
       </c>
-      <c r="Y48" s="35">
+      <c r="Y48" s="36">
         <v>35.67</v>
       </c>
-      <c r="Z48" s="33"/>
-      <c r="AA48" s="33"/>
-      <c r="AB48" s="33"/>
-      <c r="AC48" s="33"/>
-      <c r="AD48" s="33"/>
-      <c r="AE48" s="33"/>
-      <c r="AF48" s="33"/>
+      <c r="Z48" s="34"/>
+      <c r="AA48" s="34"/>
+      <c r="AB48" s="34"/>
+      <c r="AC48" s="34"/>
+      <c r="AD48" s="34"/>
+      <c r="AE48" s="34"/>
+      <c r="AF48" s="34"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="30" t="s">
-        <v>514</v>
-      </c>
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="31"/>
-      <c r="M49" s="31"/>
-      <c r="N49" s="31"/>
-      <c r="O49" s="31"/>
-      <c r="P49" s="31"/>
-      <c r="Q49" s="31"/>
-      <c r="R49" s="31"/>
-      <c r="S49" s="31"/>
-      <c r="T49" s="31"/>
-      <c r="U49" s="31"/>
-      <c r="V49" s="31"/>
-      <c r="W49" s="31"/>
-      <c r="X49" s="31"/>
-      <c r="Y49" s="31"/>
-      <c r="Z49" s="31"/>
-      <c r="AA49" s="31"/>
-      <c r="AB49" s="31"/>
-      <c r="AC49" s="31"/>
-      <c r="AD49" s="31"/>
-      <c r="AE49" s="31"/>
-      <c r="AF49" s="31"/>
+      <c r="A49" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="32"/>
+      <c r="M49" s="32"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="32"/>
+      <c r="Q49" s="32"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="32"/>
+      <c r="T49" s="32"/>
+      <c r="U49" s="32"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="32"/>
+      <c r="X49" s="32"/>
+      <c r="Y49" s="32"/>
+      <c r="Z49" s="32"/>
+      <c r="AA49" s="32"/>
+      <c r="AB49" s="32"/>
+      <c r="AC49" s="32"/>
+      <c r="AD49" s="32"/>
+      <c r="AE49" s="32"/>
+      <c r="AF49" s="32"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="32" t="s">
-        <v>515</v>
-      </c>
-      <c r="B50" s="35">
+      <c r="A50" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="B50" s="36">
         <v>7.65</v>
       </c>
-      <c r="C50" s="35">
+      <c r="C50" s="36">
         <v>6.74</v>
       </c>
-      <c r="D50" s="35">
+      <c r="D50" s="36">
         <v>6.27</v>
       </c>
-      <c r="E50" s="35">
+      <c r="E50" s="36">
         <v>4.91</v>
       </c>
-      <c r="F50" s="35">
+      <c r="F50" s="36">
         <v>6.5</v>
       </c>
-      <c r="G50" s="35">
+      <c r="G50" s="36">
         <v>5.92</v>
       </c>
-      <c r="H50" s="35">
+      <c r="H50" s="36">
         <v>6.71</v>
       </c>
-      <c r="I50" s="35">
+      <c r="I50" s="36">
         <v>6.15</v>
       </c>
-      <c r="J50" s="35">
+      <c r="J50" s="36">
         <v>7.75</v>
       </c>
-      <c r="K50" s="35">
+      <c r="K50" s="36">
         <v>8.03</v>
       </c>
-      <c r="L50" s="35">
+      <c r="L50" s="36">
         <v>8.01</v>
       </c>
-      <c r="M50" s="35">
+      <c r="M50" s="36">
         <v>7.67</v>
       </c>
-      <c r="N50" s="35">
+      <c r="N50" s="36">
         <v>28.98</v>
       </c>
-      <c r="O50" s="35">
+      <c r="O50" s="36">
         <v>13.27</v>
       </c>
-      <c r="P50" s="35">
+      <c r="P50" s="36">
         <v>5.83</v>
       </c>
-      <c r="Q50" s="35">
+      <c r="Q50" s="36">
         <v>6.53</v>
       </c>
-      <c r="R50" s="35">
+      <c r="R50" s="36">
         <v>5.12</v>
       </c>
-      <c r="S50" s="35">
+      <c r="S50" s="36">
         <v>3.81</v>
       </c>
-      <c r="T50" s="35">
+      <c r="T50" s="36">
         <v>6.02</v>
       </c>
-      <c r="U50" s="35">
+      <c r="U50" s="36">
         <v>5.58</v>
       </c>
-      <c r="V50" s="35">
+      <c r="V50" s="36">
         <v>5.45</v>
       </c>
-      <c r="W50" s="35">
+      <c r="W50" s="36">
         <v>5.44</v>
       </c>
-      <c r="X50" s="35">
+      <c r="X50" s="36">
         <v>2.7</v>
       </c>
-      <c r="Y50" s="35">
+      <c r="Y50" s="36">
         <v>2.57</v>
       </c>
-      <c r="Z50" s="35">
+      <c r="Z50" s="36">
         <v>1.83</v>
       </c>
-      <c r="AA50" s="35">
+      <c r="AA50" s="36">
         <v>0.85</v>
       </c>
-      <c r="AB50" s="35">
+      <c r="AB50" s="36">
         <v>1.93</v>
       </c>
-      <c r="AC50" s="35">
+      <c r="AC50" s="36">
         <v>1.8</v>
       </c>
-      <c r="AD50" s="35">
+      <c r="AD50" s="36">
         <v>2.23</v>
       </c>
-      <c r="AE50" s="35">
+      <c r="AE50" s="36">
         <v>2.38</v>
       </c>
-      <c r="AF50" s="35">
+      <c r="AF50" s="36">
         <v>1.57</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="32" t="s">
-        <v>516</v>
-      </c>
-      <c r="B51" s="35">
+      <c r="A51" s="33" t="s">
+        <v>518</v>
+      </c>
+      <c r="B51" s="36">
         <v>6.38</v>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="36">
         <v>6.04</v>
       </c>
-      <c r="D51" s="35">
+      <c r="D51" s="36">
         <v>5.98</v>
       </c>
-      <c r="E51" s="35">
+      <c r="E51" s="36">
         <v>5.94</v>
       </c>
-      <c r="F51" s="35">
+      <c r="F51" s="36">
         <v>6.55</v>
       </c>
-      <c r="G51" s="35">
+      <c r="G51" s="36">
         <v>6.82</v>
       </c>
-      <c r="H51" s="35">
+      <c r="H51" s="36">
         <v>7.27</v>
       </c>
-      <c r="I51" s="35">
+      <c r="I51" s="36">
         <v>7.49</v>
       </c>
-      <c r="J51" s="35">
+      <c r="J51" s="36">
         <v>9.33</v>
       </c>
-      <c r="K51" s="35">
+      <c r="K51" s="36">
         <v>10.4</v>
       </c>
-      <c r="L51" s="35">
+      <c r="L51" s="36">
         <v>9.75</v>
       </c>
-      <c r="M51" s="35">
+      <c r="M51" s="36">
         <v>9.18</v>
       </c>
-      <c r="N51" s="35">
+      <c r="N51" s="36">
         <v>8.55</v>
       </c>
-      <c r="O51" s="35">
+      <c r="O51" s="36">
         <v>6.56</v>
       </c>
-      <c r="P51" s="35">
+      <c r="P51" s="36">
         <v>5.63</v>
       </c>
-      <c r="Q51" s="35">
+      <c r="Q51" s="36">
         <v>5.58</v>
       </c>
-      <c r="R51" s="35">
+      <c r="R51" s="36">
         <v>5.32</v>
       </c>
-      <c r="S51" s="35">
+      <c r="S51" s="36">
         <v>5.38</v>
       </c>
-      <c r="T51" s="35">
+      <c r="T51" s="36">
         <v>4.94</v>
       </c>
-      <c r="U51" s="35">
+      <c r="U51" s="36">
         <v>4.31</v>
       </c>
-      <c r="V51" s="35">
+      <c r="V51" s="36">
         <v>3.39</v>
       </c>
-      <c r="W51" s="35">
+      <c r="W51" s="36">
         <v>2.18</v>
       </c>
-      <c r="X51" s="35">
+      <c r="X51" s="36">
         <v>1.78</v>
       </c>
-      <c r="Y51" s="35">
+      <c r="Y51" s="36">
         <v>1.62</v>
       </c>
-      <c r="Z51" s="35">
+      <c r="Z51" s="36">
         <v>1.61</v>
       </c>
-      <c r="AA51" s="35">
+      <c r="AA51" s="36">
         <v>1.73</v>
       </c>
-      <c r="AB51" s="35">
+      <c r="AB51" s="36">
         <v>1.99</v>
       </c>
-      <c r="AC51" s="33"/>
-      <c r="AD51" s="33"/>
-      <c r="AE51" s="33"/>
-      <c r="AF51" s="33"/>
+      <c r="AC51" s="34"/>
+      <c r="AD51" s="34"/>
+      <c r="AE51" s="34"/>
+      <c r="AF51" s="34"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
-        <v>517</v>
-      </c>
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="31"/>
-      <c r="N52" s="31"/>
-      <c r="O52" s="31"/>
-      <c r="P52" s="31"/>
-      <c r="Q52" s="31"/>
-      <c r="R52" s="31"/>
-      <c r="S52" s="31"/>
-      <c r="T52" s="31"/>
-      <c r="U52" s="31"/>
-      <c r="V52" s="31"/>
-      <c r="W52" s="31"/>
-      <c r="X52" s="31"/>
-      <c r="Y52" s="31"/>
-      <c r="Z52" s="31"/>
-      <c r="AA52" s="31"/>
-      <c r="AB52" s="31"/>
-      <c r="AC52" s="31"/>
-      <c r="AD52" s="31"/>
-      <c r="AE52" s="31"/>
-      <c r="AF52" s="31"/>
+      <c r="A52" s="31" t="s">
+        <v>519</v>
+      </c>
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="32"/>
+      <c r="N52" s="32"/>
+      <c r="O52" s="32"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="32"/>
+      <c r="R52" s="32"/>
+      <c r="S52" s="32"/>
+      <c r="T52" s="32"/>
+      <c r="U52" s="32"/>
+      <c r="V52" s="32"/>
+      <c r="W52" s="32"/>
+      <c r="X52" s="32"/>
+      <c r="Y52" s="32"/>
+      <c r="Z52" s="32"/>
+      <c r="AA52" s="32"/>
+      <c r="AB52" s="32"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="32"/>
+      <c r="AE52" s="32"/>
+      <c r="AF52" s="32"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="32" t="s">
-        <v>518</v>
-      </c>
-      <c r="B53" s="35">
+      <c r="A53" s="33" t="s">
+        <v>520</v>
+      </c>
+      <c r="B53" s="36">
         <v>16.64</v>
       </c>
-      <c r="C53" s="35">
+      <c r="C53" s="36">
         <v>12.15</v>
       </c>
-      <c r="D53" s="35">
+      <c r="D53" s="36">
         <v>13.08</v>
       </c>
-      <c r="E53" s="35">
+      <c r="E53" s="36">
         <v>9.54</v>
       </c>
-      <c r="F53" s="35">
+      <c r="F53" s="36">
         <v>18.96</v>
       </c>
-      <c r="G53" s="35">
+      <c r="G53" s="36">
         <v>15.12</v>
       </c>
-      <c r="H53" s="35">
+      <c r="H53" s="36">
         <v>18.42</v>
       </c>
-      <c r="I53" s="35">
+      <c r="I53" s="36">
         <v>16.89</v>
       </c>
-      <c r="J53" s="35">
+      <c r="J53" s="36">
         <v>22.33</v>
       </c>
-      <c r="K53" s="35">
+      <c r="K53" s="36">
         <v>20.15</v>
       </c>
-      <c r="L53" s="35">
+      <c r="L53" s="36">
         <v>23.35</v>
       </c>
-      <c r="M53" s="35">
+      <c r="M53" s="36">
         <v>16.74</v>
       </c>
-      <c r="N53" s="33"/>
-      <c r="O53" s="34">
+      <c r="N53" s="34"/>
+      <c r="O53" s="35">
         <v>101.54</v>
       </c>
-      <c r="P53" s="35">
+      <c r="P53" s="36">
         <v>10.3</v>
       </c>
-      <c r="Q53" s="35">
+      <c r="Q53" s="36">
         <v>16.04</v>
       </c>
-      <c r="R53" s="35">
+      <c r="R53" s="36">
         <v>18.25</v>
       </c>
-      <c r="S53" s="33"/>
-      <c r="T53" s="35">
+      <c r="S53" s="34"/>
+      <c r="T53" s="36">
         <v>17.49</v>
       </c>
-      <c r="U53" s="35">
+      <c r="U53" s="36">
         <v>11.01</v>
       </c>
-      <c r="V53" s="35">
+      <c r="V53" s="36">
         <v>12.52</v>
       </c>
-      <c r="W53" s="35">
+      <c r="W53" s="36">
         <v>49.45</v>
       </c>
-      <c r="X53" s="35">
+      <c r="X53" s="36">
         <v>7.78</v>
       </c>
-      <c r="Y53" s="33"/>
-      <c r="Z53" s="35">
+      <c r="Y53" s="34"/>
+      <c r="Z53" s="36">
         <v>7.09</v>
       </c>
-      <c r="AA53" s="35">
+      <c r="AA53" s="36">
         <v>2.04</v>
       </c>
-      <c r="AB53" s="35">
+      <c r="AB53" s="36">
         <v>16.09</v>
       </c>
-      <c r="AC53" s="35">
+      <c r="AC53" s="36">
         <v>6.23</v>
       </c>
-      <c r="AD53" s="35">
+      <c r="AD53" s="36">
         <v>6.64</v>
       </c>
-      <c r="AE53" s="35">
+      <c r="AE53" s="36">
         <v>7.12</v>
       </c>
-      <c r="AF53" s="35">
+      <c r="AF53" s="36">
         <v>4.95</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="32" t="s">
-        <v>519</v>
-      </c>
-      <c r="B54" s="35">
+      <c r="A54" s="33" t="s">
+        <v>521</v>
+      </c>
+      <c r="B54" s="36">
         <v>13.32</v>
       </c>
-      <c r="C54" s="35">
+      <c r="C54" s="36">
         <v>12.92</v>
       </c>
-      <c r="D54" s="35">
+      <c r="D54" s="36">
         <v>13.95</v>
       </c>
-      <c r="E54" s="35">
+      <c r="E54" s="36">
         <v>14.6</v>
       </c>
-      <c r="F54" s="35">
+      <c r="F54" s="36">
         <v>18.03</v>
       </c>
-      <c r="G54" s="35">
+      <c r="G54" s="36">
         <v>18.22</v>
       </c>
-      <c r="H54" s="35">
+      <c r="H54" s="36">
         <v>19.97</v>
       </c>
-      <c r="I54" s="35">
+      <c r="I54" s="36">
         <v>19.68</v>
       </c>
-      <c r="J54" s="35">
+      <c r="J54" s="36">
         <v>28.77</v>
       </c>
-      <c r="K54" s="35">
+      <c r="K54" s="36">
         <v>36.29</v>
       </c>
-      <c r="L54" s="35">
+      <c r="L54" s="36">
         <v>29.05</v>
       </c>
-      <c r="M54" s="35">
+      <c r="M54" s="36">
         <v>25.82</v>
       </c>
-      <c r="N54" s="35">
+      <c r="N54" s="36">
         <v>27.03</v>
       </c>
-      <c r="O54" s="35">
+      <c r="O54" s="36">
         <v>20.62</v>
       </c>
-      <c r="P54" s="35">
+      <c r="P54" s="36">
         <v>16.25</v>
       </c>
-      <c r="Q54" s="35">
+      <c r="Q54" s="36">
         <v>16.3</v>
       </c>
-      <c r="R54" s="35">
+      <c r="R54" s="36">
         <v>15.37</v>
       </c>
-      <c r="S54" s="35">
+      <c r="S54" s="36">
         <v>16.8</v>
       </c>
-      <c r="T54" s="35">
+      <c r="T54" s="36">
         <v>13.46</v>
       </c>
-      <c r="U54" s="35">
+      <c r="U54" s="36">
         <v>14.22</v>
       </c>
-      <c r="V54" s="35">
+      <c r="V54" s="36">
         <v>13.91</v>
       </c>
-      <c r="W54" s="35">
+      <c r="W54" s="36">
         <v>7.92</v>
       </c>
-      <c r="X54" s="35">
+      <c r="X54" s="36">
         <v>6.63</v>
       </c>
-      <c r="Y54" s="35">
+      <c r="Y54" s="36">
         <v>6.27</v>
       </c>
-      <c r="Z54" s="35">
+      <c r="Z54" s="36">
         <v>5.26</v>
       </c>
-      <c r="AA54" s="35">
+      <c r="AA54" s="36">
         <v>5.39</v>
       </c>
-      <c r="AB54" s="35">
+      <c r="AB54" s="36">
         <v>6.96</v>
       </c>
-      <c r="AC54" s="33"/>
-      <c r="AD54" s="33"/>
-      <c r="AE54" s="33"/>
-      <c r="AF54" s="33"/>
+      <c r="AC54" s="34"/>
+      <c r="AD54" s="34"/>
+      <c r="AE54" s="34"/>
+      <c r="AF54" s="34"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="30" t="s">
-        <v>520</v>
-      </c>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="31"/>
-      <c r="K55" s="31"/>
-      <c r="L55" s="31"/>
-      <c r="M55" s="31"/>
-      <c r="N55" s="31"/>
-      <c r="O55" s="31"/>
-      <c r="P55" s="31"/>
-      <c r="Q55" s="31"/>
-      <c r="R55" s="31"/>
-      <c r="S55" s="31"/>
-      <c r="T55" s="31"/>
-      <c r="U55" s="31"/>
-      <c r="V55" s="31"/>
-      <c r="W55" s="31"/>
-      <c r="X55" s="31"/>
-      <c r="Y55" s="31"/>
-      <c r="Z55" s="31"/>
-      <c r="AA55" s="31"/>
-      <c r="AB55" s="31"/>
-      <c r="AC55" s="31"/>
-      <c r="AD55" s="31"/>
-      <c r="AE55" s="31"/>
-      <c r="AF55" s="31"/>
+      <c r="A55" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="32"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="32"/>
+      <c r="P55" s="32"/>
+      <c r="Q55" s="32"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="32"/>
+      <c r="T55" s="32"/>
+      <c r="U55" s="32"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="32"/>
+      <c r="X55" s="32"/>
+      <c r="Y55" s="32"/>
+      <c r="Z55" s="32"/>
+      <c r="AA55" s="32"/>
+      <c r="AB55" s="32"/>
+      <c r="AC55" s="32"/>
+      <c r="AD55" s="32"/>
+      <c r="AE55" s="32"/>
+      <c r="AF55" s="32"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="32" t="s">
-        <v>521</v>
-      </c>
-      <c r="B56" s="35">
+      <c r="A56" s="33" t="s">
+        <v>523</v>
+      </c>
+      <c r="B56" s="36">
         <v>13.03</v>
       </c>
-      <c r="C56" s="35">
+      <c r="C56" s="36">
         <v>10.64</v>
       </c>
-      <c r="D56" s="35">
+      <c r="D56" s="36">
         <v>7.89</v>
       </c>
-      <c r="E56" s="35">
+      <c r="E56" s="36">
         <v>8.77</v>
       </c>
-      <c r="F56" s="35">
+      <c r="F56" s="36">
         <v>12.28</v>
       </c>
-      <c r="G56" s="35">
+      <c r="G56" s="36">
         <v>12.7</v>
       </c>
-      <c r="H56" s="35">
+      <c r="H56" s="36">
         <v>13.88</v>
       </c>
-      <c r="I56" s="35">
+      <c r="I56" s="36">
         <v>12.34</v>
       </c>
-      <c r="J56" s="35">
+      <c r="J56" s="36">
         <v>15.31</v>
       </c>
-      <c r="K56" s="35">
+      <c r="K56" s="36">
         <v>15.88</v>
       </c>
-      <c r="L56" s="35">
+      <c r="L56" s="36">
         <v>15.52</v>
       </c>
-      <c r="M56" s="35">
+      <c r="M56" s="36">
         <v>19.0</v>
       </c>
-      <c r="N56" s="33"/>
-      <c r="O56" s="35">
+      <c r="N56" s="34"/>
+      <c r="O56" s="36">
         <v>9.93</v>
       </c>
-      <c r="P56" s="35">
+      <c r="P56" s="36">
         <v>10.14</v>
       </c>
-      <c r="Q56" s="35">
+      <c r="Q56" s="36">
         <v>10.67</v>
       </c>
-      <c r="R56" s="35">
+      <c r="R56" s="36">
         <v>14.22</v>
       </c>
-      <c r="S56" s="35">
+      <c r="S56" s="36">
         <v>13.73</v>
       </c>
-      <c r="T56" s="35">
+      <c r="T56" s="36">
         <v>12.06</v>
       </c>
-      <c r="U56" s="35">
+      <c r="U56" s="36">
         <v>12.11</v>
       </c>
-      <c r="V56" s="35">
+      <c r="V56" s="36">
         <v>12.94</v>
       </c>
-      <c r="W56" s="35">
+      <c r="W56" s="36">
         <v>49.45</v>
       </c>
-      <c r="X56" s="35">
+      <c r="X56" s="36">
         <v>8.95</v>
       </c>
-      <c r="Y56" s="33"/>
-      <c r="Z56" s="35">
+      <c r="Y56" s="34"/>
+      <c r="Z56" s="36">
         <v>4.56</v>
       </c>
-      <c r="AA56" s="35">
+      <c r="AA56" s="36">
         <v>2.65</v>
       </c>
-      <c r="AB56" s="35">
+      <c r="AB56" s="36">
         <v>7.91</v>
       </c>
-      <c r="AC56" s="35">
+      <c r="AC56" s="36">
         <v>4.79</v>
       </c>
-      <c r="AD56" s="35">
+      <c r="AD56" s="36">
         <v>4.8</v>
       </c>
-      <c r="AE56" s="35">
+      <c r="AE56" s="36">
         <v>5.19</v>
       </c>
-      <c r="AF56" s="35">
+      <c r="AF56" s="36">
         <v>3.8</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="32" t="s">
-        <v>522</v>
-      </c>
-      <c r="B57" s="35">
+      <c r="A57" s="33" t="s">
+        <v>524</v>
+      </c>
+      <c r="B57" s="36">
         <v>1.57</v>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="36">
         <v>1.54</v>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="36">
         <v>1.53</v>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="36">
         <v>1.48</v>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="36">
         <v>1.53</v>
       </c>
-      <c r="G57" s="35">
+      <c r="G57" s="36">
         <v>1.54</v>
       </c>
-      <c r="H57" s="35">
+      <c r="H57" s="36">
         <v>1.48</v>
       </c>
-      <c r="I57" s="35">
+      <c r="I57" s="36">
         <v>1.41</v>
       </c>
-      <c r="J57" s="35">
+      <c r="J57" s="36">
         <v>1.49</v>
       </c>
-      <c r="K57" s="35">
+      <c r="K57" s="36">
         <v>1.48</v>
       </c>
-      <c r="L57" s="35">
+      <c r="L57" s="36">
         <v>1.36</v>
       </c>
-      <c r="M57" s="35">
+      <c r="M57" s="36">
         <v>1.34</v>
       </c>
-      <c r="N57" s="35">
+      <c r="N57" s="36">
         <v>1.26</v>
       </c>
-      <c r="O57" s="35">
+      <c r="O57" s="36">
         <v>1.06</v>
       </c>
-      <c r="P57" s="35">
+      <c r="P57" s="36">
         <v>1.0</v>
       </c>
-      <c r="Q57" s="35">
+      <c r="Q57" s="36">
         <v>1.06</v>
       </c>
-      <c r="R57" s="35">
+      <c r="R57" s="36">
         <v>1.02</v>
       </c>
-      <c r="S57" s="35">
+      <c r="S57" s="36">
         <v>1.03</v>
       </c>
-      <c r="T57" s="35">
+      <c r="T57" s="36">
         <v>1.04</v>
       </c>
-      <c r="U57" s="35">
+      <c r="U57" s="36">
         <v>0.9</v>
       </c>
-      <c r="V57" s="35">
+      <c r="V57" s="36">
         <v>0.71</v>
       </c>
-      <c r="W57" s="35">
+      <c r="W57" s="36">
         <v>0.56</v>
       </c>
-      <c r="X57" s="35">
+      <c r="X57" s="36">
         <v>0.48</v>
       </c>
-      <c r="Y57" s="35">
+      <c r="Y57" s="36">
         <v>0.45</v>
       </c>
-      <c r="Z57" s="35">
+      <c r="Z57" s="36">
         <v>0.5</v>
       </c>
-      <c r="AA57" s="35">
+      <c r="AA57" s="36">
         <v>0.59</v>
       </c>
-      <c r="AB57" s="33"/>
-      <c r="AC57" s="33"/>
-      <c r="AD57" s="33"/>
-      <c r="AE57" s="33"/>
-      <c r="AF57" s="33"/>
+      <c r="AB57" s="34"/>
+      <c r="AC57" s="34"/>
+      <c r="AD57" s="34"/>
+      <c r="AE57" s="34"/>
+      <c r="AF57" s="34"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
-        <v>523</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="31"/>
-      <c r="K58" s="31"/>
-      <c r="L58" s="31"/>
-      <c r="M58" s="31"/>
-      <c r="N58" s="31"/>
-      <c r="O58" s="31"/>
-      <c r="P58" s="31"/>
-      <c r="Q58" s="31"/>
-      <c r="R58" s="31"/>
-      <c r="S58" s="31"/>
-      <c r="T58" s="31"/>
-      <c r="U58" s="31"/>
-      <c r="V58" s="31"/>
-      <c r="W58" s="31"/>
-      <c r="X58" s="31"/>
-      <c r="Y58" s="31"/>
-      <c r="Z58" s="31"/>
-      <c r="AA58" s="31"/>
-      <c r="AB58" s="31"/>
-      <c r="AC58" s="31"/>
-      <c r="AD58" s="31"/>
-      <c r="AE58" s="31"/>
-      <c r="AF58" s="31"/>
+      <c r="A58" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="B58" s="32"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="32"/>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32"/>
+      <c r="O58" s="32"/>
+      <c r="P58" s="32"/>
+      <c r="Q58" s="32"/>
+      <c r="R58" s="32"/>
+      <c r="S58" s="32"/>
+      <c r="T58" s="32"/>
+      <c r="U58" s="32"/>
+      <c r="V58" s="32"/>
+      <c r="W58" s="32"/>
+      <c r="X58" s="32"/>
+      <c r="Y58" s="32"/>
+      <c r="Z58" s="32"/>
+      <c r="AA58" s="32"/>
+      <c r="AB58" s="32"/>
+      <c r="AC58" s="32"/>
+      <c r="AD58" s="32"/>
+      <c r="AE58" s="32"/>
+      <c r="AF58" s="32"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="32" t="s">
-        <v>524</v>
-      </c>
-      <c r="B59" s="38">
+      <c r="A59" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="B59" s="39">
         <v>-0.62</v>
       </c>
-      <c r="C59" s="35">
+      <c r="C59" s="36">
         <v>0.48</v>
       </c>
-      <c r="D59" s="38">
+      <c r="D59" s="39">
         <v>-0.9</v>
       </c>
-      <c r="E59" s="35">
+      <c r="E59" s="36">
         <v>0.08</v>
       </c>
-      <c r="F59" s="38">
+      <c r="F59" s="39">
         <v>-1.06</v>
       </c>
-      <c r="G59" s="35">
+      <c r="G59" s="36">
         <v>0.8</v>
       </c>
-      <c r="H59" s="35">
+      <c r="H59" s="36">
         <v>0.79</v>
       </c>
-      <c r="I59" s="35">
+      <c r="I59" s="36">
         <v>1.28</v>
       </c>
-      <c r="J59" s="38">
+      <c r="J59" s="39">
         <v>-1.55</v>
       </c>
-      <c r="K59" s="35">
+      <c r="K59" s="36">
         <v>0.69</v>
       </c>
-      <c r="L59" s="38">
+      <c r="L59" s="39">
         <v>-1.11</v>
       </c>
-      <c r="M59" s="35">
+      <c r="M59" s="36">
         <v>0.04</v>
       </c>
-      <c r="N59" s="33"/>
-      <c r="O59" s="38">
+      <c r="N59" s="34"/>
+      <c r="O59" s="39">
         <v>-1.17</v>
       </c>
-      <c r="P59" s="35">
+      <c r="P59" s="36">
         <v>0.46</v>
       </c>
-      <c r="Q59" s="35">
+      <c r="Q59" s="36">
         <v>0.19</v>
       </c>
-      <c r="R59" s="35">
+      <c r="R59" s="36">
         <v>0.01</v>
       </c>
-      <c r="S59" s="33"/>
-      <c r="T59" s="38">
+      <c r="S59" s="34"/>
+      <c r="T59" s="39">
         <v>-0.37</v>
       </c>
-      <c r="U59" s="35">
+      <c r="U59" s="36">
         <v>0.25</v>
       </c>
-      <c r="V59" s="35">
+      <c r="V59" s="36">
         <v>0.03</v>
       </c>
-      <c r="W59" s="38">
+      <c r="W59" s="39">
         <v>-0.62</v>
       </c>
-      <c r="X59" s="33">
+      <c r="X59" s="34">
         <v>0.0</v>
       </c>
-      <c r="Y59" s="33"/>
-      <c r="Z59" s="38">
+      <c r="Y59" s="34"/>
+      <c r="Z59" s="39">
         <v>-0.11</v>
       </c>
-      <c r="AA59" s="33">
+      <c r="AA59" s="34">
         <v>0.0</v>
       </c>
-      <c r="AB59" s="38">
+      <c r="AB59" s="39">
         <v>-0.26</v>
       </c>
-      <c r="AC59" s="38">
+      <c r="AC59" s="39">
         <v>-0.25</v>
       </c>
-      <c r="AD59" s="38">
+      <c r="AD59" s="39">
         <v>-1.37</v>
       </c>
-      <c r="AE59" s="35">
+      <c r="AE59" s="36">
         <v>0.68</v>
       </c>
-      <c r="AF59" s="33"/>
+      <c r="AF59" s="34"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="32" t="s">
-        <v>525</v>
-      </c>
-      <c r="B60" s="35">
+      <c r="A60" s="33" t="s">
+        <v>527</v>
+      </c>
+      <c r="B60" s="36">
         <v>2.03</v>
       </c>
-      <c r="C60" s="35">
+      <c r="C60" s="36">
         <v>0.74</v>
       </c>
-      <c r="D60" s="35">
+      <c r="D60" s="36">
         <v>0.82</v>
       </c>
-      <c r="E60" s="35">
+      <c r="E60" s="36">
         <v>0.61</v>
       </c>
-      <c r="F60" s="35">
+      <c r="F60" s="36">
         <v>5.72</v>
       </c>
-      <c r="G60" s="35">
+      <c r="G60" s="36">
         <v>1.41</v>
       </c>
-      <c r="H60" s="35">
+      <c r="H60" s="36">
         <v>4.94</v>
       </c>
-      <c r="I60" s="33"/>
-      <c r="J60" s="35">
+      <c r="I60" s="34"/>
+      <c r="J60" s="36">
         <v>0.83</v>
       </c>
-      <c r="K60" s="38">
+      <c r="K60" s="39">
         <v>-4.81</v>
       </c>
-      <c r="L60" s="38">
+      <c r="L60" s="39">
         <v>-3.39</v>
       </c>
-      <c r="M60" s="35">
+      <c r="M60" s="36">
         <v>3.18</v>
       </c>
-      <c r="N60" s="33"/>
-      <c r="O60" s="38">
+      <c r="N60" s="34"/>
+      <c r="O60" s="39">
         <v>-0.79</v>
       </c>
-      <c r="P60" s="38">
+      <c r="P60" s="39">
         <v>-8.04</v>
       </c>
-      <c r="Q60" s="35">
+      <c r="Q60" s="36">
         <v>13.59</v>
       </c>
-      <c r="R60" s="35">
+      <c r="R60" s="36">
         <v>0.62</v>
       </c>
-      <c r="S60" s="33"/>
-      <c r="T60" s="33"/>
-      <c r="U60" s="35">
+      <c r="S60" s="34"/>
+      <c r="T60" s="34"/>
+      <c r="U60" s="36">
         <v>1.07</v>
       </c>
-      <c r="V60" s="38">
+      <c r="V60" s="39">
         <v>-0.97</v>
       </c>
-      <c r="W60" s="38">
+      <c r="W60" s="39">
         <v>-0.87</v>
       </c>
-      <c r="X60" s="35">
+      <c r="X60" s="36">
         <v>1.78</v>
       </c>
-      <c r="Y60" s="33"/>
-      <c r="Z60" s="38">
+      <c r="Y60" s="34"/>
+      <c r="Z60" s="39">
         <v>-0.72</v>
       </c>
-      <c r="AA60" s="35">
+      <c r="AA60" s="36">
         <v>0.33</v>
       </c>
-      <c r="AB60" s="33"/>
-      <c r="AC60" s="33"/>
-      <c r="AD60" s="33"/>
-      <c r="AE60" s="33"/>
-      <c r="AF60" s="33"/>
+      <c r="AB60" s="34"/>
+      <c r="AC60" s="34"/>
+      <c r="AD60" s="34"/>
+      <c r="AE60" s="34"/>
+      <c r="AF60" s="34"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
-        <v>526</v>
-      </c>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="31"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="31"/>
-      <c r="K61" s="31"/>
-      <c r="L61" s="31"/>
-      <c r="M61" s="31"/>
-      <c r="N61" s="31"/>
-      <c r="O61" s="31"/>
-      <c r="P61" s="31"/>
-      <c r="Q61" s="31"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="31"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="31"/>
-      <c r="X61" s="31"/>
-      <c r="Y61" s="31"/>
-      <c r="Z61" s="31"/>
-      <c r="AA61" s="31"/>
-      <c r="AB61" s="31"/>
-      <c r="AC61" s="31"/>
-      <c r="AD61" s="31"/>
-      <c r="AE61" s="31"/>
-      <c r="AF61" s="31"/>
+      <c r="A61" s="31" t="s">
+        <v>528</v>
+      </c>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32"/>
+      <c r="N61" s="32"/>
+      <c r="O61" s="32"/>
+      <c r="P61" s="32"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
+      <c r="S61" s="32"/>
+      <c r="T61" s="32"/>
+      <c r="U61" s="32"/>
+      <c r="V61" s="32"/>
+      <c r="W61" s="32"/>
+      <c r="X61" s="32"/>
+      <c r="Y61" s="32"/>
+      <c r="Z61" s="32"/>
+      <c r="AA61" s="32"/>
+      <c r="AB61" s="32"/>
+      <c r="AC61" s="32"/>
+      <c r="AD61" s="32"/>
+      <c r="AE61" s="32"/>
+      <c r="AF61" s="32"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="32" t="s">
-        <v>527</v>
-      </c>
-      <c r="B62" s="35">
+      <c r="A62" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="B62" s="36">
         <v>1.26</v>
       </c>
-      <c r="C62" s="35">
+      <c r="C62" s="36">
         <v>1.13</v>
       </c>
-      <c r="D62" s="35">
+      <c r="D62" s="36">
         <v>0.93</v>
       </c>
-      <c r="E62" s="35">
+      <c r="E62" s="36">
         <v>0.84</v>
       </c>
-      <c r="F62" s="35">
+      <c r="F62" s="36">
         <v>1.1</v>
       </c>
-      <c r="G62" s="35">
+      <c r="G62" s="36">
         <v>1.15</v>
       </c>
-      <c r="H62" s="35">
+      <c r="H62" s="36">
         <v>1.08</v>
       </c>
-      <c r="I62" s="35">
+      <c r="I62" s="36">
         <v>0.88</v>
       </c>
-      <c r="J62" s="35">
+      <c r="J62" s="36">
         <v>1.0</v>
       </c>
-      <c r="K62" s="35">
+      <c r="K62" s="36">
         <v>1.07</v>
       </c>
-      <c r="L62" s="35">
+      <c r="L62" s="36">
         <v>0.99</v>
       </c>
-      <c r="M62" s="35">
+      <c r="M62" s="36">
         <v>0.95</v>
       </c>
-      <c r="N62" s="35">
+      <c r="N62" s="36">
         <v>1.06</v>
       </c>
-      <c r="O62" s="35">
+      <c r="O62" s="36">
         <v>1.06</v>
       </c>
-      <c r="P62" s="35">
+      <c r="P62" s="36">
         <v>0.88</v>
       </c>
-      <c r="Q62" s="35">
+      <c r="Q62" s="36">
         <v>1.09</v>
       </c>
-      <c r="R62" s="35">
+      <c r="R62" s="36">
         <v>0.92</v>
       </c>
-      <c r="S62" s="35">
+      <c r="S62" s="36">
         <v>0.55</v>
       </c>
-      <c r="T62" s="35">
+      <c r="T62" s="36">
         <v>0.8</v>
       </c>
-      <c r="U62" s="35">
+      <c r="U62" s="36">
         <v>0.9</v>
       </c>
-      <c r="V62" s="35">
+      <c r="V62" s="36">
         <v>0.88</v>
       </c>
-      <c r="W62" s="35">
+      <c r="W62" s="36">
         <v>0.65</v>
       </c>
-      <c r="X62" s="35">
+      <c r="X62" s="36">
         <v>0.54</v>
       </c>
-      <c r="Y62" s="35">
+      <c r="Y62" s="36">
         <v>0.46</v>
       </c>
-      <c r="Z62" s="35">
+      <c r="Z62" s="36">
         <v>0.45</v>
       </c>
-      <c r="AA62" s="35">
+      <c r="AA62" s="36">
         <v>0.4</v>
       </c>
-      <c r="AB62" s="35">
+      <c r="AB62" s="36">
         <v>0.52</v>
       </c>
-      <c r="AC62" s="35">
+      <c r="AC62" s="36">
         <v>0.53</v>
       </c>
-      <c r="AD62" s="35">
+      <c r="AD62" s="36">
         <v>0.59</v>
       </c>
-      <c r="AE62" s="35">
+      <c r="AE62" s="36">
         <v>0.7</v>
       </c>
-      <c r="AF62" s="33"/>
+      <c r="AF62" s="34"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="32" t="s">
-        <v>528</v>
-      </c>
-      <c r="B63" s="35">
+      <c r="A63" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="B63" s="36">
         <v>1.04</v>
       </c>
-      <c r="C63" s="35">
+      <c r="C63" s="36">
         <v>1.02</v>
       </c>
-      <c r="D63" s="35">
+      <c r="D63" s="36">
         <v>1.0</v>
       </c>
-      <c r="E63" s="35">
+      <c r="E63" s="36">
         <v>1.0</v>
       </c>
-      <c r="F63" s="35">
+      <c r="F63" s="36">
         <v>1.04</v>
       </c>
-      <c r="G63" s="35">
+      <c r="G63" s="36">
         <v>1.04</v>
       </c>
-      <c r="H63" s="35">
+      <c r="H63" s="36">
         <v>1.01</v>
       </c>
-      <c r="I63" s="35">
+      <c r="I63" s="36">
         <v>0.98</v>
       </c>
-      <c r="J63" s="35">
+      <c r="J63" s="36">
         <v>1.02</v>
       </c>
-      <c r="K63" s="35">
+      <c r="K63" s="36">
         <v>1.03</v>
       </c>
-      <c r="L63" s="35">
+      <c r="L63" s="36">
         <v>0.99</v>
       </c>
-      <c r="M63" s="35">
+      <c r="M63" s="36">
         <v>1.01</v>
       </c>
-      <c r="N63" s="35">
+      <c r="N63" s="36">
         <v>1.01</v>
       </c>
-      <c r="O63" s="35">
+      <c r="O63" s="36">
         <v>0.88</v>
       </c>
-      <c r="P63" s="35">
+      <c r="P63" s="36">
         <v>0.83</v>
       </c>
-      <c r="Q63" s="35">
+      <c r="Q63" s="36">
         <v>0.84</v>
       </c>
-      <c r="R63" s="35">
+      <c r="R63" s="36">
         <v>0.8</v>
       </c>
-      <c r="S63" s="35">
+      <c r="S63" s="36">
         <v>0.76</v>
       </c>
-      <c r="T63" s="35">
+      <c r="T63" s="36">
         <v>0.76</v>
       </c>
-      <c r="U63" s="35">
+      <c r="U63" s="36">
         <v>0.68</v>
       </c>
-      <c r="V63" s="35">
+      <c r="V63" s="36">
         <v>0.58</v>
       </c>
-      <c r="W63" s="35">
+      <c r="W63" s="36">
         <v>0.49</v>
       </c>
-      <c r="X63" s="35">
+      <c r="X63" s="36">
         <v>0.48</v>
       </c>
-      <c r="Y63" s="35">
+      <c r="Y63" s="36">
         <v>0.47</v>
       </c>
-      <c r="Z63" s="35">
+      <c r="Z63" s="36">
         <v>0.5</v>
       </c>
-      <c r="AA63" s="35">
+      <c r="AA63" s="36">
         <v>0.54</v>
       </c>
-      <c r="AB63" s="33"/>
-      <c r="AC63" s="33"/>
-      <c r="AD63" s="33"/>
-      <c r="AE63" s="33"/>
-      <c r="AF63" s="33"/>
+      <c r="AB63" s="34"/>
+      <c r="AC63" s="34"/>
+      <c r="AD63" s="34"/>
+      <c r="AE63" s="34"/>
+      <c r="AF63" s="34"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
-        <v>529</v>
-      </c>
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="31"/>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="31"/>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
-      <c r="X64" s="31"/>
-      <c r="Y64" s="31"/>
-      <c r="Z64" s="31"/>
-      <c r="AA64" s="31"/>
-      <c r="AB64" s="31"/>
-      <c r="AC64" s="31"/>
-      <c r="AD64" s="31"/>
-      <c r="AE64" s="31"/>
-      <c r="AF64" s="31"/>
+      <c r="A64" s="31" t="s">
+        <v>531</v>
+      </c>
+      <c r="B64" s="32"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="32"/>
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
+      <c r="X64" s="32"/>
+      <c r="Y64" s="32"/>
+      <c r="Z64" s="32"/>
+      <c r="AA64" s="32"/>
+      <c r="AB64" s="32"/>
+      <c r="AC64" s="32"/>
+      <c r="AD64" s="32"/>
+      <c r="AE64" s="32"/>
+      <c r="AF64" s="32"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="32" t="s">
-        <v>530</v>
-      </c>
-      <c r="B65" s="35">
+      <c r="A65" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="B65" s="36">
         <v>6.62</v>
       </c>
-      <c r="C65" s="35">
+      <c r="C65" s="36">
         <v>5.72</v>
       </c>
-      <c r="D65" s="35">
+      <c r="D65" s="36">
         <v>4.75</v>
       </c>
-      <c r="E65" s="35">
+      <c r="E65" s="36">
         <v>5.38</v>
       </c>
-      <c r="F65" s="35">
+      <c r="F65" s="36">
         <v>6.95</v>
       </c>
-      <c r="G65" s="35">
+      <c r="G65" s="36">
         <v>6.42</v>
       </c>
-      <c r="H65" s="35">
+      <c r="H65" s="36">
         <v>7.1</v>
       </c>
-      <c r="I65" s="35">
+      <c r="I65" s="36">
         <v>7.23</v>
       </c>
-      <c r="J65" s="35">
+      <c r="J65" s="36">
         <v>8.06</v>
       </c>
-      <c r="K65" s="35">
+      <c r="K65" s="36">
         <v>8.97</v>
       </c>
-      <c r="L65" s="35">
+      <c r="L65" s="36">
         <v>8.97</v>
       </c>
-      <c r="M65" s="35">
+      <c r="M65" s="36">
         <v>11.09</v>
       </c>
-      <c r="N65" s="35">
+      <c r="N65" s="36">
         <v>13.03</v>
       </c>
-      <c r="O65" s="35">
+      <c r="O65" s="36">
         <v>13.4</v>
       </c>
-      <c r="P65" s="35">
+      <c r="P65" s="36">
         <v>13.24</v>
       </c>
-      <c r="Q65" s="35">
+      <c r="Q65" s="36">
         <v>1.83</v>
       </c>
-      <c r="R65" s="35">
+      <c r="R65" s="36">
         <v>1.54</v>
       </c>
-      <c r="S65" s="35">
+      <c r="S65" s="36">
         <v>1.0</v>
       </c>
-      <c r="T65" s="35">
+      <c r="T65" s="36">
         <v>1.55</v>
       </c>
-      <c r="U65" s="35">
+      <c r="U65" s="36">
         <v>0.48</v>
       </c>
-      <c r="V65" s="35">
+      <c r="V65" s="36">
         <v>0.88</v>
       </c>
-      <c r="W65" s="35">
+      <c r="W65" s="36">
         <v>0.35</v>
       </c>
-      <c r="X65" s="35">
+      <c r="X65" s="36">
         <v>0.52</v>
       </c>
-      <c r="Y65" s="35">
+      <c r="Y65" s="36">
         <v>0.48</v>
       </c>
-      <c r="Z65" s="35">
+      <c r="Z65" s="36">
         <v>0.45</v>
       </c>
-      <c r="AA65" s="35">
+      <c r="AA65" s="36">
         <v>0.41</v>
       </c>
-      <c r="AB65" s="35">
+      <c r="AB65" s="36">
         <v>0.54</v>
       </c>
-      <c r="AC65" s="35">
+      <c r="AC65" s="36">
         <v>0.5</v>
       </c>
-      <c r="AD65" s="35">
+      <c r="AD65" s="36">
         <v>4.04</v>
       </c>
-      <c r="AE65" s="35">
+      <c r="AE65" s="36">
         <v>4.4</v>
       </c>
-      <c r="AF65" s="33"/>
+      <c r="AF65" s="34"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="32" t="s">
-        <v>531</v>
-      </c>
-      <c r="B66" s="35">
+      <c r="A66" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="B66" s="36">
         <v>5.78</v>
       </c>
-      <c r="C66" s="35">
+      <c r="C66" s="36">
         <v>5.72</v>
       </c>
-      <c r="D66" s="35">
+      <c r="D66" s="36">
         <v>5.94</v>
       </c>
-      <c r="E66" s="35">
+      <c r="E66" s="36">
         <v>6.5</v>
       </c>
-      <c r="F66" s="35">
+      <c r="F66" s="36">
         <v>7.09</v>
       </c>
-      <c r="G66" s="35">
+      <c r="G66" s="36">
         <v>7.43</v>
       </c>
-      <c r="H66" s="35">
+      <c r="H66" s="36">
         <v>7.96</v>
       </c>
-      <c r="I66" s="35">
+      <c r="I66" s="36">
         <v>8.64</v>
       </c>
-      <c r="J66" s="35">
+      <c r="J66" s="36">
         <v>9.66</v>
       </c>
-      <c r="K66" s="35">
+      <c r="K66" s="36">
         <v>10.73</v>
       </c>
-      <c r="L66" s="35">
+      <c r="L66" s="36">
         <v>11.64</v>
       </c>
-      <c r="M66" s="35">
+      <c r="M66" s="36">
         <v>5.59</v>
       </c>
-      <c r="N66" s="35">
+      <c r="N66" s="36">
         <v>3.64</v>
       </c>
-      <c r="O66" s="35">
+      <c r="O66" s="36">
         <v>2.3</v>
       </c>
-      <c r="P66" s="35">
+      <c r="P66" s="36">
         <v>1.76</v>
       </c>
-      <c r="Q66" s="35">
+      <c r="Q66" s="36">
         <v>1.0</v>
       </c>
-      <c r="R66" s="35">
+      <c r="R66" s="36">
         <v>0.88</v>
       </c>
-      <c r="S66" s="35">
+      <c r="S66" s="36">
         <v>0.7</v>
       </c>
-      <c r="T66" s="35">
+      <c r="T66" s="36">
         <v>0.63</v>
       </c>
-      <c r="U66" s="35">
+      <c r="U66" s="36">
         <v>0.51</v>
       </c>
-      <c r="V66" s="35">
+      <c r="V66" s="36">
         <v>0.51</v>
       </c>
-      <c r="W66" s="35">
+      <c r="W66" s="36">
         <v>0.44</v>
       </c>
-      <c r="X66" s="35">
+      <c r="X66" s="36">
         <v>0.48</v>
       </c>
-      <c r="Y66" s="35">
+      <c r="Y66" s="36">
         <v>0.48</v>
       </c>
-      <c r="Z66" s="35">
+      <c r="Z66" s="36">
         <v>0.6</v>
       </c>
-      <c r="AA66" s="35">
+      <c r="AA66" s="36">
         <v>0.81</v>
       </c>
-      <c r="AB66" s="33"/>
-      <c r="AC66" s="33"/>
-      <c r="AD66" s="33"/>
-      <c r="AE66" s="33"/>
-      <c r="AF66" s="33"/>
+      <c r="AB66" s="34"/>
+      <c r="AC66" s="34"/>
+      <c r="AD66" s="34"/>
+      <c r="AE66" s="34"/>
+      <c r="AF66" s="34"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
-        <v>532</v>
-      </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="31"/>
-      <c r="K67" s="31"/>
-      <c r="L67" s="31"/>
-      <c r="M67" s="31"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-      <c r="P67" s="31"/>
-      <c r="Q67" s="31"/>
-      <c r="R67" s="31"/>
-      <c r="S67" s="31"/>
-      <c r="T67" s="31"/>
-      <c r="U67" s="31"/>
-      <c r="V67" s="31"/>
-      <c r="W67" s="31"/>
-      <c r="X67" s="31"/>
-      <c r="Y67" s="31"/>
-      <c r="Z67" s="31"/>
-      <c r="AA67" s="31"/>
-      <c r="AB67" s="31"/>
-      <c r="AC67" s="31"/>
-      <c r="AD67" s="31"/>
-      <c r="AE67" s="31"/>
-      <c r="AF67" s="31"/>
+      <c r="A67" s="31" t="s">
+        <v>534</v>
+      </c>
+      <c r="B67" s="32"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="32"/>
+      <c r="M67" s="32"/>
+      <c r="N67" s="32"/>
+      <c r="O67" s="32"/>
+      <c r="P67" s="32"/>
+      <c r="Q67" s="32"/>
+      <c r="R67" s="32"/>
+      <c r="S67" s="32"/>
+      <c r="T67" s="32"/>
+      <c r="U67" s="32"/>
+      <c r="V67" s="32"/>
+      <c r="W67" s="32"/>
+      <c r="X67" s="32"/>
+      <c r="Y67" s="32"/>
+      <c r="Z67" s="32"/>
+      <c r="AA67" s="32"/>
+      <c r="AB67" s="32"/>
+      <c r="AC67" s="32"/>
+      <c r="AD67" s="32"/>
+      <c r="AE67" s="32"/>
+      <c r="AF67" s="32"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="32" t="s">
-        <v>533</v>
-      </c>
-      <c r="B68" s="35">
+      <c r="A68" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="B68" s="36">
         <v>9.17</v>
       </c>
-      <c r="C68" s="35">
+      <c r="C68" s="36">
         <v>6.9</v>
       </c>
-      <c r="D68" s="35">
+      <c r="D68" s="36">
         <v>5.79</v>
       </c>
-      <c r="E68" s="35">
+      <c r="E68" s="36">
         <v>7.52</v>
       </c>
-      <c r="F68" s="35">
+      <c r="F68" s="36">
         <v>13.33</v>
       </c>
-      <c r="G68" s="35">
+      <c r="G68" s="36">
         <v>7.43</v>
       </c>
-      <c r="H68" s="35">
+      <c r="H68" s="36">
         <v>7.47</v>
       </c>
-      <c r="I68" s="35">
+      <c r="I68" s="36">
         <v>10.87</v>
       </c>
-      <c r="J68" s="35">
+      <c r="J68" s="36">
         <v>12.16</v>
       </c>
-      <c r="K68" s="35">
+      <c r="K68" s="36">
         <v>9.35</v>
       </c>
-      <c r="L68" s="35">
+      <c r="L68" s="36">
         <v>9.47</v>
       </c>
-      <c r="M68" s="35">
+      <c r="M68" s="36">
         <v>27.42</v>
       </c>
-      <c r="N68" s="35">
+      <c r="N68" s="36">
         <v>11.77</v>
       </c>
-      <c r="O68" s="35">
+      <c r="O68" s="36">
         <v>13.5</v>
       </c>
-      <c r="P68" s="35">
+      <c r="P68" s="36">
         <v>11.0</v>
       </c>
-      <c r="Q68" s="35">
+      <c r="Q68" s="36">
         <v>17.88</v>
       </c>
-      <c r="R68" s="35">
+      <c r="R68" s="36">
         <v>6.36</v>
       </c>
-      <c r="S68" s="35">
+      <c r="S68" s="36">
         <v>17.6</v>
       </c>
-      <c r="T68" s="35">
+      <c r="T68" s="36">
         <v>13.29</v>
       </c>
-      <c r="U68" s="35">
+      <c r="U68" s="36">
         <v>10.77</v>
       </c>
-      <c r="V68" s="35">
+      <c r="V68" s="36">
         <v>11.68</v>
       </c>
-      <c r="W68" s="35">
+      <c r="W68" s="36">
         <v>4.27</v>
       </c>
-      <c r="X68" s="35">
+      <c r="X68" s="36">
         <v>6.81</v>
       </c>
-      <c r="Y68" s="35">
+      <c r="Y68" s="36">
         <v>4.18</v>
       </c>
-      <c r="Z68" s="35">
+      <c r="Z68" s="36">
         <v>8.96</v>
       </c>
-      <c r="AA68" s="35">
+      <c r="AA68" s="36">
         <v>4.67</v>
       </c>
-      <c r="AB68" s="35">
+      <c r="AB68" s="36">
         <v>7.37</v>
       </c>
-      <c r="AC68" s="35">
+      <c r="AC68" s="36">
         <v>10.41</v>
       </c>
-      <c r="AD68" s="35">
+      <c r="AD68" s="36">
         <v>5.61</v>
       </c>
-      <c r="AE68" s="33"/>
-      <c r="AF68" s="33"/>
+      <c r="AE68" s="34"/>
+      <c r="AF68" s="34"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="32" t="s">
-        <v>534</v>
-      </c>
-      <c r="B69" s="35">
+      <c r="A69" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="B69" s="36">
         <v>7.84</v>
       </c>
-      <c r="C69" s="35">
+      <c r="C69" s="36">
         <v>7.52</v>
       </c>
-      <c r="D69" s="35">
+      <c r="D69" s="36">
         <v>7.67</v>
       </c>
-      <c r="E69" s="35">
+      <c r="E69" s="36">
         <v>8.73</v>
       </c>
-      <c r="F69" s="35">
+      <c r="F69" s="36">
         <v>9.58</v>
       </c>
-      <c r="G69" s="35">
+      <c r="G69" s="36">
         <v>8.97</v>
       </c>
-      <c r="H69" s="35">
+      <c r="H69" s="36">
         <v>9.5</v>
       </c>
-      <c r="I69" s="35">
+      <c r="I69" s="36">
         <v>11.6</v>
       </c>
-      <c r="J69" s="35">
+      <c r="J69" s="36">
         <v>11.79</v>
       </c>
-      <c r="K69" s="35">
+      <c r="K69" s="36">
         <v>12.02</v>
       </c>
-      <c r="L69" s="35">
+      <c r="L69" s="36">
         <v>12.64</v>
       </c>
-      <c r="M69" s="35">
+      <c r="M69" s="36">
         <v>14.58</v>
       </c>
-      <c r="N69" s="35">
+      <c r="N69" s="36">
         <v>11.18</v>
       </c>
-      <c r="O69" s="35">
+      <c r="O69" s="36">
         <v>11.71</v>
       </c>
-      <c r="P69" s="35">
+      <c r="P69" s="36">
         <v>11.66</v>
       </c>
-      <c r="Q69" s="35">
+      <c r="Q69" s="36">
         <v>11.58</v>
       </c>
-      <c r="R69" s="35">
+      <c r="R69" s="36">
         <v>10.69</v>
       </c>
-      <c r="S69" s="35">
+      <c r="S69" s="36">
         <v>10.2</v>
       </c>
-      <c r="T69" s="35">
+      <c r="T69" s="36">
         <v>8.82</v>
       </c>
-      <c r="U69" s="35">
+      <c r="U69" s="36">
         <v>6.97</v>
       </c>
-      <c r="V69" s="35">
+      <c r="V69" s="36">
         <v>6.43</v>
       </c>
-      <c r="W69" s="35">
+      <c r="W69" s="36">
         <v>5.35</v>
       </c>
-      <c r="X69" s="35">
+      <c r="X69" s="36">
         <v>5.98</v>
       </c>
-      <c r="Y69" s="35">
+      <c r="Y69" s="36">
         <v>6.37</v>
       </c>
-      <c r="Z69" s="35">
+      <c r="Z69" s="36">
         <v>6.86</v>
       </c>
-      <c r="AA69" s="33"/>
-      <c r="AB69" s="33"/>
-      <c r="AC69" s="33"/>
-      <c r="AD69" s="33"/>
-      <c r="AE69" s="33"/>
-      <c r="AF69" s="33"/>
+      <c r="AA69" s="34"/>
+      <c r="AB69" s="34"/>
+      <c r="AC69" s="34"/>
+      <c r="AD69" s="34"/>
+      <c r="AE69" s="34"/>
+      <c r="AF69" s="34"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="30" t="s">
-        <v>535</v>
-      </c>
-      <c r="B70" s="31"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="31"/>
-      <c r="K70" s="31"/>
-      <c r="L70" s="31"/>
-      <c r="M70" s="31"/>
-      <c r="N70" s="31"/>
-      <c r="O70" s="31"/>
-      <c r="P70" s="31"/>
-      <c r="Q70" s="31"/>
-      <c r="R70" s="31"/>
-      <c r="S70" s="31"/>
-      <c r="T70" s="31"/>
-      <c r="U70" s="31"/>
-      <c r="V70" s="31"/>
-      <c r="W70" s="31"/>
-      <c r="X70" s="31"/>
-      <c r="Y70" s="31"/>
-      <c r="Z70" s="31"/>
-      <c r="AA70" s="31"/>
-      <c r="AB70" s="31"/>
-      <c r="AC70" s="31"/>
-      <c r="AD70" s="31"/>
-      <c r="AE70" s="31"/>
-      <c r="AF70" s="31"/>
+      <c r="A70" s="31" t="s">
+        <v>537</v>
+      </c>
+      <c r="B70" s="32"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
+      <c r="O70" s="32"/>
+      <c r="P70" s="32"/>
+      <c r="Q70" s="32"/>
+      <c r="R70" s="32"/>
+      <c r="S70" s="32"/>
+      <c r="T70" s="32"/>
+      <c r="U70" s="32"/>
+      <c r="V70" s="32"/>
+      <c r="W70" s="32"/>
+      <c r="X70" s="32"/>
+      <c r="Y70" s="32"/>
+      <c r="Z70" s="32"/>
+      <c r="AA70" s="32"/>
+      <c r="AB70" s="32"/>
+      <c r="AC70" s="32"/>
+      <c r="AD70" s="32"/>
+      <c r="AE70" s="32"/>
+      <c r="AF70" s="32"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="32" t="s">
-        <v>536</v>
-      </c>
-      <c r="B71" s="35">
+      <c r="A71" s="33" t="s">
+        <v>538</v>
+      </c>
+      <c r="B71" s="36">
         <v>19.48</v>
       </c>
-      <c r="C71" s="35">
+      <c r="C71" s="36">
         <v>10.53</v>
       </c>
-      <c r="D71" s="35">
+      <c r="D71" s="36">
         <v>9.27</v>
       </c>
-      <c r="E71" s="35">
+      <c r="E71" s="36">
         <v>14.88</v>
       </c>
-      <c r="F71" s="35">
+      <c r="F71" s="36">
         <v>57.09</v>
       </c>
-      <c r="G71" s="35">
+      <c r="G71" s="36">
         <v>15.54</v>
       </c>
-      <c r="H71" s="35">
+      <c r="H71" s="36">
         <v>15.58</v>
       </c>
-      <c r="I71" s="35">
+      <c r="I71" s="36">
         <v>38.2</v>
       </c>
-      <c r="J71" s="34">
+      <c r="J71" s="35">
         <v>133.4</v>
       </c>
-      <c r="K71" s="35">
+      <c r="K71" s="36">
         <v>43.64</v>
       </c>
-      <c r="L71" s="35">
+      <c r="L71" s="36">
         <v>33.45</v>
       </c>
-      <c r="M71" s="33"/>
-      <c r="N71" s="35">
+      <c r="M71" s="34"/>
+      <c r="N71" s="36">
         <v>36.0</v>
       </c>
-      <c r="O71" s="35">
+      <c r="O71" s="36">
         <v>55.86</v>
       </c>
-      <c r="P71" s="35">
+      <c r="P71" s="36">
         <v>24.61</v>
       </c>
-      <c r="Q71" s="35">
+      <c r="Q71" s="36">
         <v>41.11</v>
       </c>
-      <c r="R71" s="35">
+      <c r="R71" s="36">
         <v>8.84</v>
       </c>
-      <c r="S71" s="33"/>
-      <c r="T71" s="33"/>
-      <c r="U71" s="33"/>
-      <c r="V71" s="33"/>
-      <c r="W71" s="35">
+      <c r="S71" s="34"/>
+      <c r="T71" s="34"/>
+      <c r="U71" s="34"/>
+      <c r="V71" s="34"/>
+      <c r="W71" s="36">
         <v>10.92</v>
       </c>
-      <c r="X71" s="35">
+      <c r="X71" s="36">
         <v>22.36</v>
       </c>
-      <c r="Y71" s="35">
+      <c r="Y71" s="36">
         <v>11.39</v>
       </c>
-      <c r="Z71" s="33"/>
-      <c r="AA71" s="35">
+      <c r="Z71" s="34"/>
+      <c r="AA71" s="36">
         <v>32.56</v>
       </c>
-      <c r="AB71" s="35">
+      <c r="AB71" s="36">
         <v>49.77</v>
       </c>
-      <c r="AC71" s="33"/>
-      <c r="AD71" s="35">
+      <c r="AC71" s="34"/>
+      <c r="AD71" s="36">
         <v>31.38</v>
       </c>
-      <c r="AE71" s="33"/>
-      <c r="AF71" s="33"/>
+      <c r="AE71" s="34"/>
+      <c r="AF71" s="34"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="32" t="s">
-        <v>537</v>
-      </c>
-      <c r="B72" s="35">
+      <c r="A72" s="33" t="s">
+        <v>539</v>
+      </c>
+      <c r="B72" s="36">
         <v>14.6</v>
       </c>
-      <c r="C72" s="35">
+      <c r="C72" s="36">
         <v>13.96</v>
       </c>
-      <c r="D72" s="35">
+      <c r="D72" s="36">
         <v>15.41</v>
       </c>
-      <c r="E72" s="35">
+      <c r="E72" s="36">
         <v>20.5</v>
       </c>
-      <c r="F72" s="35">
+      <c r="F72" s="36">
         <v>27.08</v>
       </c>
-      <c r="G72" s="35">
+      <c r="G72" s="36">
         <v>25.92</v>
       </c>
-      <c r="H72" s="35">
+      <c r="H72" s="36">
         <v>32.01</v>
       </c>
-      <c r="I72" s="35">
+      <c r="I72" s="36">
         <v>83.68</v>
       </c>
-      <c r="J72" s="35">
+      <c r="J72" s="36">
         <v>80.9</v>
       </c>
-      <c r="K72" s="35">
+      <c r="K72" s="36">
         <v>68.8</v>
       </c>
-      <c r="L72" s="35">
+      <c r="L72" s="36">
         <v>58.06</v>
       </c>
-      <c r="M72" s="35">
+      <c r="M72" s="36">
         <v>62.22</v>
       </c>
-      <c r="N72" s="35">
+      <c r="N72" s="36">
         <v>24.1</v>
       </c>
-      <c r="O72" s="35">
+      <c r="O72" s="36">
         <v>31.05</v>
       </c>
-      <c r="P72" s="35">
+      <c r="P72" s="36">
         <v>47.88</v>
       </c>
-      <c r="Q72" s="33"/>
-      <c r="R72" s="33"/>
-      <c r="S72" s="33"/>
-      <c r="T72" s="33"/>
-      <c r="U72" s="33"/>
-      <c r="V72" s="33"/>
-      <c r="W72" s="35">
+      <c r="Q72" s="34"/>
+      <c r="R72" s="34"/>
+      <c r="S72" s="34"/>
+      <c r="T72" s="34"/>
+      <c r="U72" s="34"/>
+      <c r="V72" s="34"/>
+      <c r="W72" s="36">
         <v>23.51</v>
       </c>
-      <c r="X72" s="35">
+      <c r="X72" s="36">
         <v>34.76</v>
       </c>
-      <c r="Y72" s="35">
+      <c r="Y72" s="36">
         <v>95.69</v>
       </c>
-      <c r="Z72" s="34">
+      <c r="Z72" s="35">
         <v>3280.1</v>
       </c>
-      <c r="AA72" s="33"/>
-      <c r="AB72" s="33"/>
-      <c r="AC72" s="33"/>
-      <c r="AD72" s="33"/>
-      <c r="AE72" s="33"/>
-      <c r="AF72" s="33"/>
+      <c r="AA72" s="34"/>
+      <c r="AB72" s="34"/>
+      <c r="AC72" s="34"/>
+      <c r="AD72" s="34"/>
+      <c r="AE72" s="34"/>
+      <c r="AF72" s="34"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
